--- a/Cek Validasi.xlsx
+++ b/Cek Validasi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\icvee\ICVEE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CC26E9A-CE86-47F5-A233-33EB69698221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D703EF-BCCD-4C4B-8899-7720680DF220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9BCEFB9A-EF35-43F1-AD2F-79243D21B5CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9BCEFB9A-EF35-43F1-AD2F-79243D21B5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="315">
   <si>
     <t>accepted</t>
   </si>
@@ -814,6 +814,177 @@
   </si>
   <si>
     <t>Ada</t>
+  </si>
+  <si>
+    <t>Athif Fadheel Atharahman</t>
+  </si>
+  <si>
+    <t>Muhammad Raya Maulana, S.T</t>
+  </si>
+  <si>
+    <t>Mrs. Alya Esa Mentari</t>
+  </si>
+  <si>
+    <t>Nathanael Sitanggang; Putri Lynna A Luthan</t>
+  </si>
+  <si>
+    <t>Annisya Diaz Chandradewi, Dwi Dya Nindasari</t>
+  </si>
+  <si>
+    <t>Kurnia Chairunnisa</t>
+  </si>
+  <si>
+    <t>Albertus Andika Tri Anggoro</t>
+  </si>
+  <si>
+    <t>Putri Taqwa Prasetyaningrum</t>
+  </si>
+  <si>
+    <t>Nanditya Vianti Putri</t>
+  </si>
+  <si>
+    <t>Prof. Nathanael Sitanggang; Prof. Putri Lynna A. Luthan</t>
+  </si>
+  <si>
+    <t>Beny Prasetyo</t>
+  </si>
+  <si>
+    <t>Maskur</t>
+  </si>
+  <si>
+    <t>Putri Christianti Harefa</t>
+  </si>
+  <si>
+    <t>Stephanie Debora Assa</t>
+  </si>
+  <si>
+    <t>Veldin A. Talorete Jr.</t>
+  </si>
+  <si>
+    <t>Ramadhani Vanva Fauzia</t>
+  </si>
+  <si>
+    <t>Mifta Nur Farid</t>
+  </si>
+  <si>
+    <t>Aditya Sheva Pratama</t>
+  </si>
+  <si>
+    <t>Nurwahid Rahman</t>
+  </si>
+  <si>
+    <t>Mohammad Noer Dafiq</t>
+  </si>
+  <si>
+    <t>DAVE SHANNA MARIE E. GIGAWIN &amp; JOHN PAUL L. ULLEGUE</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Chandra Restu Pradipto, Aloysius Bernanda Gunawan, Bambang Pratama</t>
+  </si>
+  <si>
+    <t>Muhammad Fahry Ali</t>
+  </si>
+  <si>
+    <t>Dr. I Nyoman Kusuma Wardana</t>
+  </si>
+  <si>
+    <t>Muhammad Andika Fadilla, S.Kom</t>
+  </si>
+  <si>
+    <t>Dr. Hendy Briantoro</t>
+  </si>
+  <si>
+    <t>Lintang Deni Laksana</t>
+  </si>
+  <si>
+    <t>Mr. Fajar Romadhan</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Ir. Nathanael Sitanggang, S.T. M.Pd.</t>
+  </si>
+  <si>
+    <t>Ir. Erika Loniza, S.T., M.Eng</t>
+  </si>
+  <si>
+    <t>Afandi Sahputra, S.T., M.T.</t>
+  </si>
+  <si>
+    <t>Hamid Rahman, M.Kom.</t>
+  </si>
+  <si>
+    <t>Dr.Ir.Putri Taqwa Prasetyaningrum,S.T.,M.T</t>
+  </si>
+  <si>
+    <t>Febri Liantoni, S.ST., M.Kom</t>
+  </si>
+  <si>
+    <t>: Juris Vassa Ivandro, S.Kom</t>
+  </si>
+  <si>
+    <t>Anisa Dzulkarnain, S.Kom., M.Kom.</t>
+  </si>
+  <si>
+    <t>SUGITO, S.Kom</t>
+  </si>
+  <si>
+    <t>rais nurwahyudin</t>
+  </si>
+  <si>
+    <t>Prof. Dr. Ir. Putri Lynna A. Luthan, M.Sc</t>
+  </si>
+  <si>
+    <t>Sugeng Hari Wibowo</t>
+  </si>
+  <si>
+    <t>Beny Prasetyo, S.Kom., M.Kom</t>
+  </si>
+  <si>
+    <t>Maskur, S.Kom., M.Kom</t>
+  </si>
+  <si>
+    <t>Fauziyah Wafa'Abdillah, S.Tr.T.</t>
+  </si>
+  <si>
+    <t>Mochamad Nizar Palefi Ma'ady, S.Kom., M.Kom., M.IM</t>
+  </si>
+  <si>
+    <t>Mr. Veldin A. Talorete Jr.</t>
+  </si>
+  <si>
+    <t>Mochamad Nizar Palefi Ma’ady, S.Kom., M.Kom., M.IM</t>
+  </si>
+  <si>
+    <t>Mifta Nur Farid, S.T., M.T.</t>
+  </si>
+  <si>
+    <t>Febri Liantoni</t>
+  </si>
+  <si>
+    <t>Eric Julianto</t>
+  </si>
+  <si>
+    <t>Sritrusta Sukaridhoto ,ST., Ph.D.</t>
+  </si>
+  <si>
+    <t>Eko Puji Laksono, S.Kom.,M.Kom</t>
+  </si>
+  <si>
+    <t>DAVE SHANNA MARIE E. GIGAWIN</t>
+  </si>
+  <si>
+    <t>Hastupara Amurwojakti</t>
+  </si>
+  <si>
+    <t>Fadli Sirait, S.Si, M.T, Ph.D</t>
+  </si>
+  <si>
+    <t>Aditya Alpha Theodore, S.Pd.</t>
+  </si>
+  <si>
+    <t>Abdullah Billman</t>
   </si>
 </sst>
 </file>
@@ -1187,4589 +1358,5098 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8EC83B3-BC2A-4809-B2F8-BB2F25E0028C}">
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:L127"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="137.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="158.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="78.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="137.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="158.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="78.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1">
+        <f>IF(A1="Ada", 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
       <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
+      <c r="G1" s="1">
+        <v>46247</v>
       </c>
       <c r="H1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B2)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B2" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C2)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B2" t="str">
+        <f>IF(A2="Ada",IF(IFERROR(VLOOKUP(C2,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C2,Sheet2!A:C,3,FALSE),""),VLOOKUP(C2,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C2" s="2">
         <v>1571257569</v>
       </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
       <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G2" t="s">
-        <v>3</v>
+      <c r="G2" s="1">
+        <v>46247</v>
       </c>
       <c r="H2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B3)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B3" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C3)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B3" t="str">
+        <f>IF(A3="Ada",IF(IFERROR(VLOOKUP(C3,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C3,Sheet2!A:C,3,FALSE),""),VLOOKUP(C3,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C3" s="2">
         <v>1571267469</v>
       </c>
-      <c r="C3" t="s">
-        <v>0</v>
-      </c>
       <c r="D3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3</v>
+      <c r="G3" s="1">
+        <v>46247</v>
       </c>
       <c r="H3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B4)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B4" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C4)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B4" t="str">
+        <f>IF(A4="Ada",IF(IFERROR(VLOOKUP(C4,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C4,Sheet2!A:C,3,FALSE),""),VLOOKUP(C4,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="2">
         <v>1571267484</v>
       </c>
-      <c r="C4" t="s">
-        <v>0</v>
-      </c>
       <c r="D4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G4" t="s">
-        <v>3</v>
+      <c r="G4" s="1">
+        <v>46247</v>
       </c>
       <c r="H4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B5)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C5)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" t="str">
+        <f>IF(A5="Ada",IF(IFERROR(VLOOKUP(C5,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C5,Sheet2!A:C,3,FALSE),""),VLOOKUP(C5,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Athif Fadheel Atharahman</v>
+      </c>
+      <c r="C5" s="2">
         <v>1571267967</v>
       </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
       <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G5" t="s">
-        <v>3</v>
+      <c r="G5" s="1">
+        <v>46247</v>
       </c>
       <c r="H5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B6)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B6" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C6)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B6" t="str">
+        <f>IF(A6="Ada",IF(IFERROR(VLOOKUP(C6,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C6,Sheet2!A:C,3,FALSE),""),VLOOKUP(C6,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C6" s="2">
         <v>1571268176</v>
       </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
       <c r="D6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G6" t="s">
-        <v>3</v>
+      <c r="G6" s="1">
+        <v>46247</v>
       </c>
       <c r="H6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B7)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B7" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C7)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B7" t="str">
+        <f>IF(A7="Ada",IF(IFERROR(VLOOKUP(C7,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C7,Sheet2!A:C,3,FALSE),""),VLOOKUP(C7,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="2">
         <v>1571273336</v>
       </c>
-      <c r="C7" t="s">
-        <v>0</v>
-      </c>
       <c r="D7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G7" t="s">
-        <v>3</v>
+      <c r="G7" s="1">
+        <v>46247</v>
       </c>
       <c r="H7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B8)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C8)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" t="str">
+        <f>IF(A8="Ada",IF(IFERROR(VLOOKUP(C8,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C8,Sheet2!A:C,3,FALSE),""),VLOOKUP(C8,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Dr. I Nyoman Kusuma Wardana</v>
+      </c>
+      <c r="C8" s="2">
         <v>1571279780</v>
       </c>
-      <c r="C8" t="s">
-        <v>0</v>
-      </c>
       <c r="D8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G8" t="s">
-        <v>3</v>
+      <c r="G8" s="1">
+        <v>46247</v>
       </c>
       <c r="H8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B9)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B9" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C9)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B9" t="str">
+        <f>IF(A9="Ada",IF(IFERROR(VLOOKUP(C9,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C9,Sheet2!A:C,3,FALSE),""),VLOOKUP(C9,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C9" s="2">
         <v>1571280074</v>
       </c>
-      <c r="C9" t="s">
-        <v>0</v>
-      </c>
       <c r="D9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G9" t="s">
-        <v>3</v>
+      <c r="G9" s="1">
+        <v>46247</v>
       </c>
       <c r="H9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B10)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B10" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C10)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B10" t="str">
+        <f>IF(A10="Ada",IF(IFERROR(VLOOKUP(C10,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C10,Sheet2!A:C,3,FALSE),""),VLOOKUP(C10,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="2">
         <v>1571280332</v>
       </c>
-      <c r="C10" t="s">
-        <v>0</v>
-      </c>
       <c r="D10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
         <v>22</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G10" t="s">
-        <v>3</v>
+      <c r="G10" s="1">
+        <v>46247</v>
       </c>
       <c r="H10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B11)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B11" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C11)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B11" t="str">
+        <f>IF(A11="Ada",IF(IFERROR(VLOOKUP(C11,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C11,Sheet2!A:C,3,FALSE),""),VLOOKUP(C11,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="2">
         <v>1571281021</v>
       </c>
-      <c r="C11" t="s">
-        <v>0</v>
-      </c>
       <c r="D11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
         <v>24</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G11" t="s">
-        <v>3</v>
+      <c r="G11" s="1">
+        <v>46247</v>
       </c>
       <c r="H11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B12)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B12" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C12)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B12" t="str">
+        <f>IF(A12="Ada",IF(IFERROR(VLOOKUP(C12,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C12,Sheet2!A:C,3,FALSE),""),VLOOKUP(C12,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="2">
         <v>1571281084</v>
       </c>
-      <c r="C12" t="s">
-        <v>0</v>
-      </c>
       <c r="D12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
         <v>26</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G12" t="s">
-        <v>3</v>
+      <c r="G12" s="1">
+        <v>46247</v>
       </c>
       <c r="H12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B13)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C13)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" t="str">
+        <f>IF(A13="Ada",IF(IFERROR(VLOOKUP(C13,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C13,Sheet2!A:C,3,FALSE),""),VLOOKUP(C13,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Afandi Sahputra, S.T., M.T.</v>
+      </c>
+      <c r="C13" s="2">
         <v>1571282959</v>
       </c>
-      <c r="C13" t="s">
-        <v>0</v>
-      </c>
       <c r="D13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
         <v>28</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G13" t="s">
-        <v>3</v>
+      <c r="G13" s="1">
+        <v>46247</v>
       </c>
       <c r="H13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B14)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B14" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C14)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B14" t="str">
+        <f>IF(A14="Ada",IF(IFERROR(VLOOKUP(C14,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C14,Sheet2!A:C,3,FALSE),""),VLOOKUP(C14,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="2">
         <v>1571284761</v>
       </c>
-      <c r="C14" t="s">
-        <v>0</v>
-      </c>
       <c r="D14" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G14" t="s">
-        <v>3</v>
+      <c r="G14" s="1">
+        <v>46247</v>
       </c>
       <c r="H14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B15)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B15" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C15)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B15" t="str">
+        <f>IF(A15="Ada",IF(IFERROR(VLOOKUP(C15,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C15,Sheet2!A:C,3,FALSE),""),VLOOKUP(C15,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="2">
         <v>1571286979</v>
       </c>
-      <c r="C15" t="s">
-        <v>0</v>
-      </c>
       <c r="D15" t="s">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
         <v>32</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G15" t="s">
-        <v>3</v>
+      <c r="G15" s="1">
+        <v>46247</v>
       </c>
       <c r="H15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B16)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B16" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C16)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B16" t="str">
+        <f>IF(A16="Ada",IF(IFERROR(VLOOKUP(C16,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C16,Sheet2!A:C,3,FALSE),""),VLOOKUP(C16,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="2">
         <v>1571287902</v>
       </c>
-      <c r="C16" t="s">
-        <v>0</v>
-      </c>
       <c r="D16" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
         <v>34</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G16" t="s">
-        <v>3</v>
+      <c r="G16" s="1">
+        <v>46247</v>
       </c>
       <c r="H16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B17)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C17)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" t="str">
+        <f>IF(A17="Ada",IF(IFERROR(VLOOKUP(C17,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C17,Sheet2!A:C,3,FALSE),""),VLOOKUP(C17,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Eko Puji Laksono, S.Kom.,M.Kom</v>
+      </c>
+      <c r="C17" s="2">
         <v>1571289829</v>
       </c>
-      <c r="C17" t="s">
-        <v>0</v>
-      </c>
       <c r="D17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
         <v>36</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G17" t="s">
-        <v>3</v>
+      <c r="G17" s="1">
+        <v>46247</v>
       </c>
       <c r="H17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B18)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C18)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" t="str">
+        <f>IF(A18="Ada",IF(IFERROR(VLOOKUP(C18,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C18,Sheet2!A:C,3,FALSE),""),VLOOKUP(C18,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Nathanael Sitanggang; Putri Lynna A Luthan</v>
+      </c>
+      <c r="C18" s="2">
         <v>1571290388</v>
       </c>
-      <c r="C18" t="s">
-        <v>0</v>
-      </c>
       <c r="D18" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
         <v>38</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G18" t="s">
-        <v>3</v>
+      <c r="G18" s="1">
+        <v>46247</v>
       </c>
       <c r="H18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B19)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B19" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C19)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B19" t="str">
+        <f>IF(A19="Ada",IF(IFERROR(VLOOKUP(C19,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C19,Sheet2!A:C,3,FALSE),""),VLOOKUP(C19,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="2">
         <v>1571290492</v>
       </c>
-      <c r="C19" t="s">
-        <v>0</v>
-      </c>
       <c r="D19" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
         <v>40</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G19" t="s">
-        <v>3</v>
+      <c r="G19" s="1">
+        <v>46247</v>
       </c>
       <c r="H19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B20)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C20)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" t="str">
+        <f>IF(A20="Ada",IF(IFERROR(VLOOKUP(C20,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C20,Sheet2!A:C,3,FALSE),""),VLOOKUP(C20,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Dr. Hendy Briantoro</v>
+      </c>
+      <c r="C20" s="2">
         <v>1571290818</v>
       </c>
-      <c r="C20" t="s">
-        <v>0</v>
-      </c>
       <c r="D20" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
         <v>42</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G20" t="s">
-        <v>3</v>
+      <c r="G20" s="1">
+        <v>46247</v>
       </c>
       <c r="H20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B21)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B21" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C21)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B21" t="str">
+        <f>IF(A21="Ada",IF(IFERROR(VLOOKUP(C21,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C21,Sheet2!A:C,3,FALSE),""),VLOOKUP(C21,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="2">
         <v>1571291145</v>
       </c>
-      <c r="C21" t="s">
-        <v>0</v>
-      </c>
       <c r="D21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
         <v>44</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G21" t="s">
-        <v>3</v>
+      <c r="G21" s="1">
+        <v>46247</v>
       </c>
       <c r="H21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B22)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B22" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C22)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B22" t="str">
+        <f>IF(A22="Ada",IF(IFERROR(VLOOKUP(C22,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C22,Sheet2!A:C,3,FALSE),""),VLOOKUP(C22,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="2">
         <v>1571291163</v>
       </c>
-      <c r="C22" t="s">
-        <v>0</v>
-      </c>
       <c r="D22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
         <v>46</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G22" t="s">
-        <v>3</v>
+      <c r="G22" s="1">
+        <v>46247</v>
       </c>
       <c r="H22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B23)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B23" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C23)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B23" t="str">
+        <f>IF(A23="Ada",IF(IFERROR(VLOOKUP(C23,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C23,Sheet2!A:C,3,FALSE),""),VLOOKUP(C23,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="2">
         <v>1571291272</v>
       </c>
-      <c r="C23" t="s">
-        <v>0</v>
-      </c>
       <c r="D23" t="s">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
         <v>48</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G23" t="s">
-        <v>3</v>
+      <c r="G23" s="1">
+        <v>46247</v>
       </c>
       <c r="H23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B24)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C24)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" t="str">
+        <f>IF(A24="Ada",IF(IFERROR(VLOOKUP(C24,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C24,Sheet2!A:C,3,FALSE),""),VLOOKUP(C24,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Hamid Rahman, M.Kom.</v>
+      </c>
+      <c r="C24" s="2">
         <v>1571291423</v>
       </c>
-      <c r="C24" t="s">
-        <v>0</v>
-      </c>
       <c r="D24" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
         <v>50</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G24" t="s">
-        <v>3</v>
+      <c r="G24" s="1">
+        <v>46247</v>
       </c>
       <c r="H24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B25)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C25)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" t="str">
+        <f>IF(A25="Ada",IF(IFERROR(VLOOKUP(C25,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C25,Sheet2!A:C,3,FALSE),""),VLOOKUP(C25,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>DAVE SHANNA MARIE E. GIGAWIN &amp; JOHN PAUL L. ULLEGUE</v>
+      </c>
+      <c r="C25" s="2">
         <v>1571291625</v>
       </c>
-      <c r="C25" t="s">
-        <v>0</v>
-      </c>
       <c r="D25" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
         <v>52</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G25" t="s">
-        <v>3</v>
+      <c r="G25" s="1">
+        <v>46247</v>
       </c>
       <c r="H25" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B26)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C26)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" t="str">
+        <f>IF(A26="Ada",IF(IFERROR(VLOOKUP(C26,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C26,Sheet2!A:C,3,FALSE),""),VLOOKUP(C26,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Eric Julianto</v>
+      </c>
+      <c r="C26" s="2">
         <v>1571291638</v>
       </c>
-      <c r="C26" t="s">
-        <v>0</v>
-      </c>
       <c r="D26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
         <v>54</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>55</v>
       </c>
-      <c r="F26" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G26" t="s">
-        <v>3</v>
+      <c r="G26" s="1">
+        <v>46247</v>
       </c>
       <c r="H26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B27)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C27)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" t="str">
+        <f>IF(A27="Ada",IF(IFERROR(VLOOKUP(C27,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C27,Sheet2!A:C,3,FALSE),""),VLOOKUP(C27,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Annisya Diaz Chandradewi, Dwi Dya Nindasari</v>
+      </c>
+      <c r="C27" s="2">
         <v>1571291668</v>
       </c>
-      <c r="C27" t="s">
-        <v>0</v>
-      </c>
       <c r="D27" t="s">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
         <v>56</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G27" t="s">
-        <v>3</v>
+      <c r="G27" s="1">
+        <v>46247</v>
       </c>
       <c r="H27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B28)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B28" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C28)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B28" t="str">
+        <f>IF(A28="Ada",IF(IFERROR(VLOOKUP(C28,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C28,Sheet2!A:C,3,FALSE),""),VLOOKUP(C28,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="2">
         <v>1571291739</v>
       </c>
-      <c r="C28" t="s">
-        <v>0</v>
-      </c>
       <c r="D28" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" t="s">
         <v>58</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G28" t="s">
-        <v>3</v>
+      <c r="G28" s="1">
+        <v>46247</v>
       </c>
       <c r="H28" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B29)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B29" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C29)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B29" t="str">
+        <f>IF(A29="Ada",IF(IFERROR(VLOOKUP(C29,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C29,Sheet2!A:C,3,FALSE),""),VLOOKUP(C29,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="2">
         <v>1571291753</v>
       </c>
-      <c r="C29" t="s">
-        <v>0</v>
-      </c>
       <c r="D29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
         <v>60</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>61</v>
       </c>
-      <c r="F29" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G29" t="s">
-        <v>3</v>
+      <c r="G29" s="1">
+        <v>46247</v>
       </c>
       <c r="H29" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K29" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B30)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B30" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C30)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B30" t="str">
+        <f>IF(A30="Ada",IF(IFERROR(VLOOKUP(C30,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C30,Sheet2!A:C,3,FALSE),""),VLOOKUP(C30,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="2">
         <v>1571291857</v>
       </c>
-      <c r="C30" t="s">
-        <v>0</v>
-      </c>
       <c r="D30" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" t="s">
         <v>62</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>63</v>
       </c>
-      <c r="F30" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G30" t="s">
-        <v>3</v>
+      <c r="G30" s="1">
+        <v>46247</v>
       </c>
       <c r="H30" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B31)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C31)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" t="str">
+        <f>IF(A31="Ada",IF(IFERROR(VLOOKUP(C31,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C31,Sheet2!A:C,3,FALSE),""),VLOOKUP(C31,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Veldin A. Talorete Jr.</v>
+      </c>
+      <c r="C31" s="2">
         <v>1571291877</v>
       </c>
-      <c r="C31" t="s">
-        <v>0</v>
-      </c>
       <c r="D31" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
         <v>64</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>65</v>
       </c>
-      <c r="F31" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G31" t="s">
-        <v>3</v>
+      <c r="G31" s="1">
+        <v>46247</v>
       </c>
       <c r="H31" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B32)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B32" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C32)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B32" t="str">
+        <f>IF(A32="Ada",IF(IFERROR(VLOOKUP(C32,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C32,Sheet2!A:C,3,FALSE),""),VLOOKUP(C32,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="2">
         <v>1571291893</v>
       </c>
-      <c r="C32" t="s">
-        <v>0</v>
-      </c>
       <c r="D32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
         <v>66</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>67</v>
       </c>
-      <c r="F32" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G32" t="s">
-        <v>3</v>
+      <c r="G32" s="1">
+        <v>46247</v>
       </c>
       <c r="H32" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B33)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C33)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" t="str">
+        <f>IF(A33="Ada",IF(IFERROR(VLOOKUP(C33,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C33,Sheet2!A:C,3,FALSE),""),VLOOKUP(C33,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Fauziyah Wafa'Abdillah, S.Tr.T.</v>
+      </c>
+      <c r="C33" s="2">
         <v>1571291935</v>
       </c>
-      <c r="C33" t="s">
-        <v>0</v>
-      </c>
       <c r="D33" t="s">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
         <v>68</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>69</v>
       </c>
-      <c r="F33" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G33" t="s">
-        <v>3</v>
+      <c r="G33" s="1">
+        <v>46247</v>
       </c>
       <c r="H33" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B34)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B34" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C34)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B34" t="str">
+        <f>IF(A34="Ada",IF(IFERROR(VLOOKUP(C34,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C34,Sheet2!A:C,3,FALSE),""),VLOOKUP(C34,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="2">
         <v>1571292019</v>
       </c>
-      <c r="C34" t="s">
-        <v>0</v>
-      </c>
       <c r="D34" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
         <v>70</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>71</v>
       </c>
-      <c r="F34" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G34" t="s">
-        <v>3</v>
+      <c r="G34" s="1">
+        <v>46247</v>
       </c>
       <c r="H34" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B35)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B35" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C35)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B35" t="str">
+        <f>IF(A35="Ada",IF(IFERROR(VLOOKUP(C35,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C35,Sheet2!A:C,3,FALSE),""),VLOOKUP(C35,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="2">
         <v>1571292191</v>
       </c>
-      <c r="C35" t="s">
-        <v>0</v>
-      </c>
       <c r="D35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
         <v>72</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G35" t="s">
-        <v>3</v>
+      <c r="G35" s="1">
+        <v>46247</v>
       </c>
       <c r="H35" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K35" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B36)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B36" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C36)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B36" t="str">
+        <f>IF(A36="Ada",IF(IFERROR(VLOOKUP(C36,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C36,Sheet2!A:C,3,FALSE),""),VLOOKUP(C36,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="2">
         <v>1571292198</v>
       </c>
-      <c r="C36" t="s">
-        <v>0</v>
-      </c>
       <c r="D36" t="s">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
         <v>74</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G36" t="s">
-        <v>3</v>
+      <c r="G36" s="1">
+        <v>46247</v>
       </c>
       <c r="H36" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I36" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B37)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B37" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C37)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B37" t="str">
+        <f>IF(A37="Ada",IF(IFERROR(VLOOKUP(C37,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C37,Sheet2!A:C,3,FALSE),""),VLOOKUP(C37,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="2">
         <v>1571292256</v>
       </c>
-      <c r="C37" t="s">
-        <v>0</v>
-      </c>
       <c r="D37" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
         <v>76</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>77</v>
       </c>
-      <c r="F37" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G37" t="s">
-        <v>3</v>
+      <c r="G37" s="1">
+        <v>46247</v>
       </c>
       <c r="H37" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K37" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B38)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B38" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C38)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B38" t="str">
+        <f>IF(A38="Ada",IF(IFERROR(VLOOKUP(C38,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C38,Sheet2!A:C,3,FALSE),""),VLOOKUP(C38,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="2">
         <v>1571292300</v>
       </c>
-      <c r="C38" t="s">
-        <v>0</v>
-      </c>
       <c r="D38" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" t="s">
         <v>78</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>79</v>
       </c>
-      <c r="F38" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G38" t="s">
-        <v>3</v>
+      <c r="G38" s="1">
+        <v>46247</v>
       </c>
       <c r="H38" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B39)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B39" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C39)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B39" t="str">
+        <f>IF(A39="Ada",IF(IFERROR(VLOOKUP(C39,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C39,Sheet2!A:C,3,FALSE),""),VLOOKUP(C39,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="2">
         <v>1571292314</v>
       </c>
-      <c r="C39" t="s">
-        <v>0</v>
-      </c>
       <c r="D39" t="s">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
         <v>80</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>81</v>
       </c>
-      <c r="F39" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G39" t="s">
-        <v>3</v>
+      <c r="G39" s="1">
+        <v>46247</v>
       </c>
       <c r="H39" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I39" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K39" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B40)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B40" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C40)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B40" t="str">
+        <f>IF(A40="Ada",IF(IFERROR(VLOOKUP(C40,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C40,Sheet2!A:C,3,FALSE),""),VLOOKUP(C40,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="2">
         <v>1571292356</v>
       </c>
-      <c r="C40" t="s">
-        <v>0</v>
-      </c>
       <c r="D40" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
         <v>82</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>83</v>
       </c>
-      <c r="F40" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G40" t="s">
-        <v>3</v>
+      <c r="G40" s="1">
+        <v>46247</v>
       </c>
       <c r="H40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B41)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B41" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C41)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B41" t="str">
+        <f>IF(A41="Ada",IF(IFERROR(VLOOKUP(C41,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C41,Sheet2!A:C,3,FALSE),""),VLOOKUP(C41,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="2">
         <v>1571292389</v>
       </c>
-      <c r="C41" t="s">
-        <v>0</v>
-      </c>
       <c r="D41" t="s">
+        <v>0</v>
+      </c>
+      <c r="E41" t="s">
         <v>84</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>85</v>
       </c>
-      <c r="F41" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G41" t="s">
-        <v>3</v>
+      <c r="G41" s="1">
+        <v>46247</v>
       </c>
       <c r="H41" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I41" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K41" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B42)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B42" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C42)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B42" t="str">
+        <f>IF(A42="Ada",IF(IFERROR(VLOOKUP(C42,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C42,Sheet2!A:C,3,FALSE),""),VLOOKUP(C42,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="2">
         <v>1571292412</v>
       </c>
-      <c r="C42" t="s">
-        <v>0</v>
-      </c>
       <c r="D42" t="s">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
         <v>86</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>87</v>
       </c>
-      <c r="F42" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G42" t="s">
-        <v>3</v>
+      <c r="G42" s="1">
+        <v>46247</v>
       </c>
       <c r="H42" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I42" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B43)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B43" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C43)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B43" t="str">
+        <f>IF(A43="Ada",IF(IFERROR(VLOOKUP(C43,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C43,Sheet2!A:C,3,FALSE),""),VLOOKUP(C43,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="2">
         <v>1571292417</v>
       </c>
-      <c r="C43" t="s">
-        <v>0</v>
-      </c>
       <c r="D43" t="s">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
         <v>88</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>89</v>
       </c>
-      <c r="F43" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G43" t="s">
-        <v>3</v>
+      <c r="G43" s="1">
+        <v>46247</v>
       </c>
       <c r="H43" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K43" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B44)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C44)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" t="str">
+        <f>IF(A44="Ada",IF(IFERROR(VLOOKUP(C44,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C44,Sheet2!A:C,3,FALSE),""),VLOOKUP(C44,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Muhammad Andika Fadilla, S.Kom</v>
+      </c>
+      <c r="C44" s="2">
         <v>1571294926</v>
       </c>
-      <c r="C44" t="s">
-        <v>0</v>
-      </c>
       <c r="D44" t="s">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
         <v>90</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>91</v>
       </c>
-      <c r="F44" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G44" t="s">
-        <v>3</v>
+      <c r="G44" s="1">
+        <v>46247</v>
       </c>
       <c r="H44" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K44" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B45)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B45" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C45)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B45" t="str">
+        <f>IF(A45="Ada",IF(IFERROR(VLOOKUP(C45,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C45,Sheet2!A:C,3,FALSE),""),VLOOKUP(C45,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="2">
         <v>1571295664</v>
       </c>
-      <c r="C45" t="s">
-        <v>0</v>
-      </c>
       <c r="D45" t="s">
+        <v>0</v>
+      </c>
+      <c r="E45" t="s">
         <v>92</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>93</v>
       </c>
-      <c r="F45" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G45" t="s">
-        <v>3</v>
+      <c r="G45" s="1">
+        <v>46247</v>
       </c>
       <c r="H45" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I45" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K45" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B46)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B46" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C46)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B46" t="str">
+        <f>IF(A46="Ada",IF(IFERROR(VLOOKUP(C46,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C46,Sheet2!A:C,3,FALSE),""),VLOOKUP(C46,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="2">
         <v>1571295713</v>
       </c>
-      <c r="C46" t="s">
-        <v>0</v>
-      </c>
       <c r="D46" t="s">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
         <v>94</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>95</v>
       </c>
-      <c r="F46" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G46" t="s">
-        <v>3</v>
+      <c r="G46" s="1">
+        <v>46247</v>
       </c>
       <c r="H46" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I46" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K46" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B47)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C47)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" t="str">
+        <f>IF(A47="Ada",IF(IFERROR(VLOOKUP(C47,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C47,Sheet2!A:C,3,FALSE),""),VLOOKUP(C47,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Beny Prasetyo</v>
+      </c>
+      <c r="C47" s="2">
         <v>1571296305</v>
       </c>
-      <c r="C47" t="s">
-        <v>0</v>
-      </c>
       <c r="D47" t="s">
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
         <v>96</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>97</v>
       </c>
-      <c r="F47" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G47" t="s">
-        <v>3</v>
+      <c r="G47" s="1">
+        <v>46247</v>
       </c>
       <c r="H47" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I47" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K47" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B48)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B48" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C48)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B48" t="str">
+        <f>IF(A48="Ada",IF(IFERROR(VLOOKUP(C48,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C48,Sheet2!A:C,3,FALSE),""),VLOOKUP(C48,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="2">
         <v>1571296467</v>
       </c>
-      <c r="C48" t="s">
-        <v>0</v>
-      </c>
       <c r="D48" t="s">
+        <v>0</v>
+      </c>
+      <c r="E48" t="s">
         <v>98</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>99</v>
       </c>
-      <c r="F48" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G48" t="s">
-        <v>3</v>
+      <c r="G48" s="1">
+        <v>46247</v>
       </c>
       <c r="H48" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I48" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K48" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B49)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B49" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C49)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B49" t="str">
+        <f>IF(A49="Ada",IF(IFERROR(VLOOKUP(C49,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C49,Sheet2!A:C,3,FALSE),""),VLOOKUP(C49,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="2">
         <v>1571296538</v>
       </c>
-      <c r="C49" t="s">
-        <v>0</v>
-      </c>
       <c r="D49" t="s">
+        <v>0</v>
+      </c>
+      <c r="E49" t="s">
         <v>100</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>101</v>
       </c>
-      <c r="F49" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G49" t="s">
-        <v>3</v>
+      <c r="G49" s="1">
+        <v>46247</v>
       </c>
       <c r="H49" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I49" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K49" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B50)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B50" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C50)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B50" t="str">
+        <f>IF(A50="Ada",IF(IFERROR(VLOOKUP(C50,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C50,Sheet2!A:C,3,FALSE),""),VLOOKUP(C50,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="2">
         <v>1571296859</v>
       </c>
-      <c r="C50" t="s">
-        <v>0</v>
-      </c>
       <c r="D50" t="s">
+        <v>0</v>
+      </c>
+      <c r="E50" t="s">
         <v>102</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>103</v>
       </c>
-      <c r="F50" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G50" t="s">
-        <v>3</v>
+      <c r="G50" s="1">
+        <v>46247</v>
       </c>
       <c r="H50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I50" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K50" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B51)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C51)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" t="str">
+        <f>IF(A51="Ada",IF(IFERROR(VLOOKUP(C51,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C51,Sheet2!A:C,3,FALSE),""),VLOOKUP(C51,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Nanditya Vianti Putri</v>
+      </c>
+      <c r="C51" s="2">
         <v>1571297897</v>
       </c>
-      <c r="C51" t="s">
-        <v>0</v>
-      </c>
       <c r="D51" t="s">
+        <v>0</v>
+      </c>
+      <c r="E51" t="s">
         <v>104</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>105</v>
       </c>
-      <c r="F51" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G51" t="s">
-        <v>3</v>
+      <c r="G51" s="1">
+        <v>46247</v>
       </c>
       <c r="H51" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I51" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K51" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L51" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B52)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B52" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C52)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B52" t="str">
+        <f>IF(A52="Ada",IF(IFERROR(VLOOKUP(C52,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C52,Sheet2!A:C,3,FALSE),""),VLOOKUP(C52,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="2">
         <v>1571298038</v>
       </c>
-      <c r="C52" t="s">
-        <v>0</v>
-      </c>
       <c r="D52" t="s">
+        <v>0</v>
+      </c>
+      <c r="E52" t="s">
         <v>106</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>107</v>
       </c>
-      <c r="F52" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G52" t="s">
-        <v>3</v>
+      <c r="G52" s="1">
+        <v>46247</v>
       </c>
       <c r="H52" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I52" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K52" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L52" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B53)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C53)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" t="str">
+        <f>IF(A53="Ada",IF(IFERROR(VLOOKUP(C53,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C53,Sheet2!A:C,3,FALSE),""),VLOOKUP(C53,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Sugeng Hari Wibowo</v>
+      </c>
+      <c r="C53" s="2">
         <v>1571298045</v>
       </c>
-      <c r="C53" t="s">
-        <v>0</v>
-      </c>
       <c r="D53" t="s">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
         <v>108</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>109</v>
       </c>
-      <c r="F53" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G53" t="s">
-        <v>3</v>
+      <c r="G53" s="1">
+        <v>46247</v>
       </c>
       <c r="H53" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I53" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K53" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L53" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B54)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C54)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" t="str">
+        <f>IF(A54="Ada",IF(IFERROR(VLOOKUP(C54,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C54,Sheet2!A:C,3,FALSE),""),VLOOKUP(C54,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>SUGITO, S.Kom</v>
+      </c>
+      <c r="C54" s="2">
         <v>1571298209</v>
       </c>
-      <c r="C54" t="s">
-        <v>0</v>
-      </c>
       <c r="D54" t="s">
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
         <v>110</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>111</v>
       </c>
-      <c r="F54" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G54" t="s">
-        <v>3</v>
+      <c r="G54" s="1">
+        <v>46247</v>
       </c>
       <c r="H54" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I54" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L54" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B55)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B55" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C55)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B55" t="str">
+        <f>IF(A55="Ada",IF(IFERROR(VLOOKUP(C55,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C55,Sheet2!A:C,3,FALSE),""),VLOOKUP(C55,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="2">
         <v>1571298211</v>
       </c>
-      <c r="C55" t="s">
-        <v>0</v>
-      </c>
       <c r="D55" t="s">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
         <v>112</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>113</v>
       </c>
-      <c r="F55" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G55" t="s">
-        <v>3</v>
+      <c r="G55" s="1">
+        <v>46247</v>
       </c>
       <c r="H55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I55" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L55" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B56)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B56" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C56)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B56" t="str">
+        <f>IF(A56="Ada",IF(IFERROR(VLOOKUP(C56,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C56,Sheet2!A:C,3,FALSE),""),VLOOKUP(C56,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="2">
         <v>1571298278</v>
       </c>
-      <c r="C56" t="s">
-        <v>0</v>
-      </c>
       <c r="D56" t="s">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
         <v>114</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>115</v>
       </c>
-      <c r="F56" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G56" t="s">
-        <v>3</v>
+      <c r="G56" s="1">
+        <v>46247</v>
       </c>
       <c r="H56" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L56" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B57)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B57" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C57)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B57" t="str">
+        <f>IF(A57="Ada",IF(IFERROR(VLOOKUP(C57,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C57,Sheet2!A:C,3,FALSE),""),VLOOKUP(C57,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C57" s="2">
         <v>1571298336</v>
       </c>
-      <c r="C57" t="s">
-        <v>0</v>
-      </c>
       <c r="D57" t="s">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
         <v>116</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>117</v>
       </c>
-      <c r="F57" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G57" t="s">
-        <v>3</v>
+      <c r="G57" s="1">
+        <v>46247</v>
       </c>
       <c r="H57" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I57" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K57" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L57" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B58)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B58" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C58)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B58" t="str">
+        <f>IF(A58="Ada",IF(IFERROR(VLOOKUP(C58,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C58,Sheet2!A:C,3,FALSE),""),VLOOKUP(C58,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C58" s="2">
         <v>1571298391</v>
       </c>
-      <c r="C58" t="s">
-        <v>0</v>
-      </c>
       <c r="D58" t="s">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
         <v>118</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>119</v>
       </c>
-      <c r="F58" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G58" t="s">
-        <v>3</v>
+      <c r="G58" s="1">
+        <v>46247</v>
       </c>
       <c r="H58" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I58" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K58" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L58" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B59)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C59)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" t="str">
+        <f>IF(A59="Ada",IF(IFERROR(VLOOKUP(C59,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C59,Sheet2!A:C,3,FALSE),""),VLOOKUP(C59,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Maskur</v>
+      </c>
+      <c r="C59" s="2">
         <v>1571298458</v>
       </c>
-      <c r="C59" t="s">
-        <v>0</v>
-      </c>
       <c r="D59" t="s">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
         <v>120</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>121</v>
       </c>
-      <c r="F59" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G59" t="s">
-        <v>3</v>
+      <c r="G59" s="1">
+        <v>46247</v>
       </c>
       <c r="H59" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I59" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K59" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L59" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B60)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B60" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C60)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B60" t="str">
+        <f>IF(A60="Ada",IF(IFERROR(VLOOKUP(C60,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C60,Sheet2!A:C,3,FALSE),""),VLOOKUP(C60,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C60" s="2">
         <v>1571298491</v>
       </c>
-      <c r="C60" t="s">
-        <v>0</v>
-      </c>
       <c r="D60" t="s">
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
         <v>122</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>123</v>
       </c>
-      <c r="F60" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G60" t="s">
-        <v>3</v>
+      <c r="G60" s="1">
+        <v>46247</v>
       </c>
       <c r="H60" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I60" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J60" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L60" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B61)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B61" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C61)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B61" t="str">
+        <f>IF(A61="Ada",IF(IFERROR(VLOOKUP(C61,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C61,Sheet2!A:C,3,FALSE),""),VLOOKUP(C61,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="2">
         <v>1571298535</v>
       </c>
-      <c r="C61" t="s">
-        <v>0</v>
-      </c>
       <c r="D61" t="s">
+        <v>0</v>
+      </c>
+      <c r="E61" t="s">
         <v>124</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>125</v>
       </c>
-      <c r="F61" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G61" t="s">
-        <v>3</v>
+      <c r="G61" s="1">
+        <v>46247</v>
       </c>
       <c r="H61" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I61" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J61" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K61" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L61" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B62)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B62" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C62)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B62" t="str">
+        <f>IF(A62="Ada",IF(IFERROR(VLOOKUP(C62,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C62,Sheet2!A:C,3,FALSE),""),VLOOKUP(C62,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="2">
         <v>1571298550</v>
       </c>
-      <c r="C62" t="s">
-        <v>0</v>
-      </c>
       <c r="D62" t="s">
+        <v>0</v>
+      </c>
+      <c r="E62" t="s">
         <v>126</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>127</v>
       </c>
-      <c r="F62" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G62" t="s">
-        <v>3</v>
+      <c r="G62" s="1">
+        <v>46247</v>
       </c>
       <c r="H62" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I62" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J62" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K62" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B63)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C63)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" t="str">
+        <f>IF(A63="Ada",IF(IFERROR(VLOOKUP(C63,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C63,Sheet2!A:C,3,FALSE),""),VLOOKUP(C63,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Anisa Dzulkarnain, S.Kom., M.Kom.</v>
+      </c>
+      <c r="C63" s="2">
         <v>1571298558</v>
       </c>
-      <c r="C63" t="s">
-        <v>0</v>
-      </c>
       <c r="D63" t="s">
+        <v>0</v>
+      </c>
+      <c r="E63" t="s">
         <v>128</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>129</v>
       </c>
-      <c r="F63" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G63" t="s">
-        <v>3</v>
+      <c r="G63" s="1">
+        <v>46247</v>
       </c>
       <c r="H63" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I63" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K63" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B64)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B64" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C64)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B64" t="str">
+        <f>IF(A64="Ada",IF(IFERROR(VLOOKUP(C64,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C64,Sheet2!A:C,3,FALSE),""),VLOOKUP(C64,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C64" s="2">
         <v>1571298670</v>
       </c>
-      <c r="C64" t="s">
-        <v>0</v>
-      </c>
       <c r="D64" t="s">
+        <v>0</v>
+      </c>
+      <c r="E64" t="s">
         <v>130</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>131</v>
       </c>
-      <c r="F64" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G64" t="s">
-        <v>3</v>
+      <c r="G64" s="1">
+        <v>46247</v>
       </c>
       <c r="H64" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I64" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J64" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B65)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B65" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C65)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B65" t="str">
+        <f>IF(A65="Ada",IF(IFERROR(VLOOKUP(C65,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C65,Sheet2!A:C,3,FALSE),""),VLOOKUP(C65,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C65" s="2">
         <v>1571298839</v>
       </c>
-      <c r="C65" t="s">
-        <v>0</v>
-      </c>
       <c r="D65" t="s">
+        <v>0</v>
+      </c>
+      <c r="E65" t="s">
         <v>132</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>133</v>
       </c>
-      <c r="F65" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G65" t="s">
-        <v>3</v>
+      <c r="G65" s="1">
+        <v>46247</v>
       </c>
       <c r="H65" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I65" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J65" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K65" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B66)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C66)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" t="str">
+        <f>IF(A66="Ada",IF(IFERROR(VLOOKUP(C66,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C66,Sheet2!A:C,3,FALSE),""),VLOOKUP(C66,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Mr. Fajar Romadhan</v>
+      </c>
+      <c r="C66" s="2">
         <v>1571298976</v>
       </c>
-      <c r="C66" t="s">
-        <v>0</v>
-      </c>
       <c r="D66" t="s">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s">
         <v>134</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>135</v>
       </c>
-      <c r="F66" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G66" t="s">
-        <v>3</v>
+      <c r="G66" s="1">
+        <v>46247</v>
       </c>
       <c r="H66" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I66" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J66" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K66" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B67)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B67" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C67)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B67" t="str">
+        <f>IF(A67="Ada",IF(IFERROR(VLOOKUP(C67,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C67,Sheet2!A:C,3,FALSE),""),VLOOKUP(C67,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C67" s="2">
         <v>1571299336</v>
       </c>
-      <c r="C67" t="s">
-        <v>0</v>
-      </c>
       <c r="D67" t="s">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
         <v>136</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>137</v>
       </c>
-      <c r="F67" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G67" t="s">
-        <v>3</v>
+      <c r="G67" s="1">
+        <v>46247</v>
       </c>
       <c r="H67" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J67" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K67" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B68)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C68)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" t="str">
+        <f>IF(A68="Ada",IF(IFERROR(VLOOKUP(C68,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C68,Sheet2!A:C,3,FALSE),""),VLOOKUP(C68,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Chandra Restu Pradipto, Aloysius Bernanda Gunawan, Bambang Pratama</v>
+      </c>
+      <c r="C68" s="2">
         <v>1571300264</v>
       </c>
-      <c r="C68" t="s">
-        <v>0</v>
-      </c>
       <c r="D68" t="s">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
         <v>138</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>139</v>
       </c>
-      <c r="F68" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G68" t="s">
-        <v>3</v>
+      <c r="G68" s="1">
+        <v>46247</v>
       </c>
       <c r="H68" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I68" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J68" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K68" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B69)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B69" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C69)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B69" t="str">
+        <f>IF(A69="Ada",IF(IFERROR(VLOOKUP(C69,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C69,Sheet2!A:C,3,FALSE),""),VLOOKUP(C69,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C69" s="2">
         <v>1571300636</v>
       </c>
-      <c r="C69" t="s">
-        <v>0</v>
-      </c>
       <c r="D69" t="s">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
         <v>140</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>141</v>
       </c>
-      <c r="F69" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G69" t="s">
-        <v>3</v>
+      <c r="G69" s="1">
+        <v>46247</v>
       </c>
       <c r="H69" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I69" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J69" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K69" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B70)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C70)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" t="str">
+        <f>IF(A70="Ada",IF(IFERROR(VLOOKUP(C70,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C70,Sheet2!A:C,3,FALSE),""),VLOOKUP(C70,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Albertus Andika Tri Anggoro</v>
+      </c>
+      <c r="C70" s="2">
         <v>1571300706</v>
       </c>
-      <c r="C70" t="s">
-        <v>0</v>
-      </c>
       <c r="D70" t="s">
+        <v>0</v>
+      </c>
+      <c r="E70" t="s">
         <v>142</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>143</v>
       </c>
-      <c r="F70" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G70" t="s">
-        <v>3</v>
+      <c r="G70" s="1">
+        <v>46247</v>
       </c>
       <c r="H70" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I70" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J70" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K70" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B71)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B71" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C71)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B71" t="str">
+        <f>IF(A71="Ada",IF(IFERROR(VLOOKUP(C71,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C71,Sheet2!A:C,3,FALSE),""),VLOOKUP(C71,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C71" s="2">
         <v>1571301191</v>
       </c>
-      <c r="C71" t="s">
-        <v>0</v>
-      </c>
       <c r="D71" t="s">
+        <v>0</v>
+      </c>
+      <c r="E71" t="s">
         <v>144</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>145</v>
       </c>
-      <c r="F71" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G71" t="s">
-        <v>3</v>
+      <c r="G71" s="1">
+        <v>46247</v>
       </c>
       <c r="H71" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I71" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K71" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L71" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B72)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B72" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C72)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B72" t="str">
+        <f>IF(A72="Ada",IF(IFERROR(VLOOKUP(C72,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C72,Sheet2!A:C,3,FALSE),""),VLOOKUP(C72,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C72" s="2">
         <v>1571301987</v>
       </c>
-      <c r="C72" t="s">
-        <v>0</v>
-      </c>
       <c r="D72" t="s">
+        <v>0</v>
+      </c>
+      <c r="E72" t="s">
         <v>146</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>147</v>
       </c>
-      <c r="F72" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G72" t="s">
-        <v>3</v>
+      <c r="G72" s="1">
+        <v>46247</v>
       </c>
       <c r="H72" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I72" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K72" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L72" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B73)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C73)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" t="str">
+        <f>IF(A73="Ada",IF(IFERROR(VLOOKUP(C73,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C73,Sheet2!A:C,3,FALSE),""),VLOOKUP(C73,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Kurnia Chairunnisa</v>
+      </c>
+      <c r="C73" s="2">
         <v>1571303126</v>
       </c>
-      <c r="C73" t="s">
-        <v>0</v>
-      </c>
       <c r="D73" t="s">
+        <v>0</v>
+      </c>
+      <c r="E73" t="s">
         <v>148</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>149</v>
       </c>
-      <c r="F73" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G73" t="s">
-        <v>3</v>
+      <c r="G73" s="1">
+        <v>46247</v>
       </c>
       <c r="H73" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I73" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K73" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L73" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B74)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C74)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" t="str">
+        <f>IF(A74="Ada",IF(IFERROR(VLOOKUP(C74,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C74,Sheet2!A:C,3,FALSE),""),VLOOKUP(C74,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Aditya Sheva Pratama</v>
+      </c>
+      <c r="C74" s="2">
         <v>1571304164</v>
       </c>
-      <c r="C74" t="s">
-        <v>0</v>
-      </c>
       <c r="D74" t="s">
+        <v>0</v>
+      </c>
+      <c r="E74" t="s">
         <v>150</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>151</v>
       </c>
-      <c r="F74" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G74" t="s">
-        <v>3</v>
+      <c r="G74" s="1">
+        <v>46247</v>
       </c>
       <c r="H74" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I74" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K74" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L74" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B75)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B75" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C75)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Ada</v>
+      </c>
+      <c r="B75" t="str">
+        <f>IF(A75="Ada",IF(IFERROR(VLOOKUP(C75,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C75,Sheet2!A:C,3,FALSE),""),VLOOKUP(C75,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Muhammad Fahry Ali</v>
+      </c>
+      <c r="C75" s="2">
         <v>1571304167</v>
       </c>
-      <c r="C75" t="s">
-        <v>0</v>
-      </c>
       <c r="D75" t="s">
+        <v>0</v>
+      </c>
+      <c r="E75" t="s">
         <v>152</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>153</v>
       </c>
-      <c r="F75" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G75" t="s">
-        <v>3</v>
+      <c r="G75" s="1">
+        <v>46247</v>
       </c>
       <c r="H75" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I75" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K75" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L75" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B76)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B76" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C76)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B76" t="str">
+        <f>IF(A76="Ada",IF(IFERROR(VLOOKUP(C76,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C76,Sheet2!A:C,3,FALSE),""),VLOOKUP(C76,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C76" s="2">
         <v>1571304299</v>
       </c>
-      <c r="C76" t="s">
-        <v>0</v>
-      </c>
       <c r="D76" t="s">
+        <v>0</v>
+      </c>
+      <c r="E76" t="s">
         <v>154</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>155</v>
       </c>
-      <c r="F76" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G76" t="s">
-        <v>3</v>
+      <c r="G76" s="1">
+        <v>46247</v>
       </c>
       <c r="H76" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J76" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K76" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B77)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B77" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C77)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B77" t="str">
+        <f>IF(A77="Ada",IF(IFERROR(VLOOKUP(C77,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C77,Sheet2!A:C,3,FALSE),""),VLOOKUP(C77,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C77" s="2">
         <v>1571304412</v>
       </c>
-      <c r="C77" t="s">
-        <v>0</v>
-      </c>
       <c r="D77" t="s">
+        <v>0</v>
+      </c>
+      <c r="E77" t="s">
         <v>156</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>157</v>
       </c>
-      <c r="F77" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G77" t="s">
-        <v>3</v>
+      <c r="G77" s="1">
+        <v>46247</v>
       </c>
       <c r="H77" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I77" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J77" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K77" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L77" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B78)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B78" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C78)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B78" t="str">
+        <f>IF(A78="Ada",IF(IFERROR(VLOOKUP(C78,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C78,Sheet2!A:C,3,FALSE),""),VLOOKUP(C78,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C78" s="2">
         <v>1571304421</v>
       </c>
-      <c r="C78" t="s">
-        <v>0</v>
-      </c>
       <c r="D78" t="s">
+        <v>0</v>
+      </c>
+      <c r="E78" t="s">
         <v>158</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>159</v>
       </c>
-      <c r="F78" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G78" t="s">
-        <v>3</v>
+      <c r="G78" s="1">
+        <v>46247</v>
       </c>
       <c r="H78" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I78" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J78" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K78" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L78" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B79)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B79" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C79)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B79" t="str">
+        <f>IF(A79="Ada",IF(IFERROR(VLOOKUP(C79,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C79,Sheet2!A:C,3,FALSE),""),VLOOKUP(C79,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C79" s="2">
         <v>1571304705</v>
       </c>
-      <c r="C79" t="s">
-        <v>0</v>
-      </c>
       <c r="D79" t="s">
+        <v>0</v>
+      </c>
+      <c r="E79" t="s">
         <v>160</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>161</v>
       </c>
-      <c r="F79" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G79" t="s">
-        <v>3</v>
+      <c r="G79" s="1">
+        <v>46247</v>
       </c>
       <c r="H79" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I79" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J79" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K79" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L79" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B80)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B80" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C80)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B80" t="str">
+        <f>IF(A80="Ada",IF(IFERROR(VLOOKUP(C80,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C80,Sheet2!A:C,3,FALSE),""),VLOOKUP(C80,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="2">
         <v>1571304827</v>
       </c>
-      <c r="C80" t="s">
-        <v>0</v>
-      </c>
       <c r="D80" t="s">
+        <v>0</v>
+      </c>
+      <c r="E80" t="s">
         <v>162</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>163</v>
       </c>
-      <c r="F80" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G80" t="s">
-        <v>3</v>
+      <c r="G80" s="1">
+        <v>46247</v>
       </c>
       <c r="H80" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I80" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J80" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K80" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L80" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B81)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C81)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" t="str">
+        <f>IF(A81="Ada",IF(IFERROR(VLOOKUP(C81,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C81,Sheet2!A:C,3,FALSE),""),VLOOKUP(C81,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Putri Christianti Harefa</v>
+      </c>
+      <c r="C81" s="2">
         <v>1571305122</v>
       </c>
-      <c r="C81" t="s">
-        <v>0</v>
-      </c>
       <c r="D81" t="s">
+        <v>0</v>
+      </c>
+      <c r="E81" t="s">
         <v>164</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>165</v>
       </c>
-      <c r="F81" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G81" t="s">
-        <v>3</v>
+      <c r="G81" s="1">
+        <v>46247</v>
       </c>
       <c r="H81" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I81" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J81" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K81" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L81" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B82)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B82" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C82)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B82" t="str">
+        <f>IF(A82="Ada",IF(IFERROR(VLOOKUP(C82,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C82,Sheet2!A:C,3,FALSE),""),VLOOKUP(C82,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="2">
         <v>1571305134</v>
       </c>
-      <c r="C82" t="s">
-        <v>0</v>
-      </c>
       <c r="D82" t="s">
+        <v>0</v>
+      </c>
+      <c r="E82" t="s">
         <v>166</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>167</v>
       </c>
-      <c r="F82" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G82" t="s">
-        <v>3</v>
+      <c r="G82" s="1">
+        <v>46247</v>
       </c>
       <c r="H82" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I82" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J82" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K82" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L82" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B83)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B83" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C83)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B83" t="str">
+        <f>IF(A83="Ada",IF(IFERROR(VLOOKUP(C83,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C83,Sheet2!A:C,3,FALSE),""),VLOOKUP(C83,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="2">
         <v>1571305135</v>
       </c>
-      <c r="C83" t="s">
-        <v>0</v>
-      </c>
       <c r="D83" t="s">
+        <v>0</v>
+      </c>
+      <c r="E83" t="s">
         <v>168</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>169</v>
       </c>
-      <c r="F83" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G83" t="s">
-        <v>3</v>
+      <c r="G83" s="1">
+        <v>46247</v>
       </c>
       <c r="H83" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I83" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J83" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K83" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L83" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B84)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C84)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" t="str">
+        <f>IF(A84="Ada",IF(IFERROR(VLOOKUP(C84,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C84,Sheet2!A:C,3,FALSE),""),VLOOKUP(C84,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Mifta Nur Farid</v>
+      </c>
+      <c r="C84" s="2">
         <v>1571305199</v>
       </c>
-      <c r="C84" t="s">
-        <v>0</v>
-      </c>
       <c r="D84" t="s">
+        <v>0</v>
+      </c>
+      <c r="E84" t="s">
         <v>170</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>171</v>
       </c>
-      <c r="F84" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G84" t="s">
-        <v>3</v>
+      <c r="G84" s="1">
+        <v>46247</v>
       </c>
       <c r="H84" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I84" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J84" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K84" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L84" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B85)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B85" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C85)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B85" t="str">
+        <f>IF(A85="Ada",IF(IFERROR(VLOOKUP(C85,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C85,Sheet2!A:C,3,FALSE),""),VLOOKUP(C85,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="2">
         <v>1571305278</v>
       </c>
-      <c r="C85" t="s">
-        <v>0</v>
-      </c>
       <c r="D85" t="s">
+        <v>0</v>
+      </c>
+      <c r="E85" t="s">
         <v>172</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>173</v>
       </c>
-      <c r="F85" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G85" t="s">
-        <v>3</v>
+      <c r="G85" s="1">
+        <v>46247</v>
       </c>
       <c r="H85" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J85" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K85" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L85" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B86)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B86" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C86)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B86" t="str">
+        <f>IF(A86="Ada",IF(IFERROR(VLOOKUP(C86,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C86,Sheet2!A:C,3,FALSE),""),VLOOKUP(C86,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="2">
         <v>1571305279</v>
       </c>
-      <c r="C86" t="s">
-        <v>0</v>
-      </c>
       <c r="D86" t="s">
+        <v>0</v>
+      </c>
+      <c r="E86" t="s">
         <v>174</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>175</v>
       </c>
-      <c r="F86" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G86" t="s">
-        <v>3</v>
+      <c r="G86" s="1">
+        <v>46247</v>
       </c>
       <c r="H86" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I86" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J86" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K86" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L86" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B87)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C87)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" t="str">
+        <f>IF(A87="Ada",IF(IFERROR(VLOOKUP(C87,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C87,Sheet2!A:C,3,FALSE),""),VLOOKUP(C87,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Hastupara Amurwojakti</v>
+      </c>
+      <c r="C87" s="2">
         <v>1571305316</v>
       </c>
-      <c r="C87" t="s">
-        <v>0</v>
-      </c>
       <c r="D87" t="s">
+        <v>0</v>
+      </c>
+      <c r="E87" t="s">
         <v>176</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>177</v>
       </c>
-      <c r="F87" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G87" t="s">
-        <v>3</v>
+      <c r="G87" s="1">
+        <v>46247</v>
       </c>
       <c r="H87" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I87" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J87" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K87" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L87" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B88)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C88)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B88" s="2">
+      <c r="B88" t="str">
+        <f>IF(A88="Ada",IF(IFERROR(VLOOKUP(C88,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C88,Sheet2!A:C,3,FALSE),""),VLOOKUP(C88,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Mrs. Alya Esa Mentari</v>
+      </c>
+      <c r="C88" s="2">
         <v>1571305337</v>
       </c>
-      <c r="C88" t="s">
-        <v>0</v>
-      </c>
       <c r="D88" t="s">
+        <v>0</v>
+      </c>
+      <c r="E88" t="s">
         <v>178</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>179</v>
       </c>
-      <c r="F88" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G88" t="s">
-        <v>3</v>
+      <c r="G88" s="1">
+        <v>46247</v>
       </c>
       <c r="H88" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I88" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J88" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K88" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L88" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B89)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C89)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B89" s="2">
+      <c r="B89" t="str">
+        <f>IF(A89="Ada",IF(IFERROR(VLOOKUP(C89,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C89,Sheet2!A:C,3,FALSE),""),VLOOKUP(C89,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Ramadhani Vanva Fauzia</v>
+      </c>
+      <c r="C89" s="2">
         <v>1571305354</v>
       </c>
-      <c r="C89" t="s">
-        <v>0</v>
-      </c>
       <c r="D89" t="s">
+        <v>0</v>
+      </c>
+      <c r="E89" t="s">
         <v>180</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>181</v>
       </c>
-      <c r="F89" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G89" t="s">
-        <v>3</v>
+      <c r="G89" s="1">
+        <v>46247</v>
       </c>
       <c r="H89" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I89" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J89" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K89" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L89" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B90)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C90)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B90" s="2">
+      <c r="B90" t="str">
+        <f>IF(A90="Ada",IF(IFERROR(VLOOKUP(C90,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C90,Sheet2!A:C,3,FALSE),""),VLOOKUP(C90,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Stephanie Debora Assa</v>
+      </c>
+      <c r="C90" s="2">
         <v>1571305360</v>
       </c>
-      <c r="C90" t="s">
-        <v>0</v>
-      </c>
       <c r="D90" t="s">
+        <v>0</v>
+      </c>
+      <c r="E90" t="s">
         <v>182</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>183</v>
       </c>
-      <c r="F90" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G90" t="s">
-        <v>3</v>
+      <c r="G90" s="1">
+        <v>46247</v>
       </c>
       <c r="H90" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I90" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J90" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K90" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L90" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B91)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B91" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C91)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B91" t="str">
+        <f>IF(A91="Ada",IF(IFERROR(VLOOKUP(C91,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C91,Sheet2!A:C,3,FALSE),""),VLOOKUP(C91,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C91" s="2">
         <v>1571305396</v>
       </c>
-      <c r="C91" t="s">
-        <v>0</v>
-      </c>
       <c r="D91" t="s">
+        <v>0</v>
+      </c>
+      <c r="E91" t="s">
         <v>184</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>185</v>
       </c>
-      <c r="F91" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G91" t="s">
-        <v>3</v>
+      <c r="G91" s="1">
+        <v>46247</v>
       </c>
       <c r="H91" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I91" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J91" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K91" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L91" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B92)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B92" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C92)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B92" t="str">
+        <f>IF(A92="Ada",IF(IFERROR(VLOOKUP(C92,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C92,Sheet2!A:C,3,FALSE),""),VLOOKUP(C92,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C92" s="2">
         <v>1571305460</v>
       </c>
-      <c r="C92" t="s">
-        <v>0</v>
-      </c>
       <c r="D92" t="s">
+        <v>0</v>
+      </c>
+      <c r="E92" t="s">
         <v>186</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>187</v>
       </c>
-      <c r="F92" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G92" t="s">
-        <v>3</v>
+      <c r="G92" s="1">
+        <v>46247</v>
       </c>
       <c r="H92" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I92" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J92" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K92" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L92" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B93)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C93)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B93" s="2">
+      <c r="B93" t="str">
+        <f>IF(A93="Ada",IF(IFERROR(VLOOKUP(C93,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C93,Sheet2!A:C,3,FALSE),""),VLOOKUP(C93,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>: Juris Vassa Ivandro, S.Kom</v>
+      </c>
+      <c r="C93" s="2">
         <v>1571305741</v>
       </c>
-      <c r="C93" t="s">
-        <v>0</v>
-      </c>
       <c r="D93" t="s">
+        <v>0</v>
+      </c>
+      <c r="E93" t="s">
         <v>188</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>189</v>
       </c>
-      <c r="F93" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G93" t="s">
-        <v>3</v>
+      <c r="G93" s="1">
+        <v>46247</v>
       </c>
       <c r="H93" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I93" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J93" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K93" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L93" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B94)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B94" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C94)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B94" t="str">
+        <f>IF(A94="Ada",IF(IFERROR(VLOOKUP(C94,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C94,Sheet2!A:C,3,FALSE),""),VLOOKUP(C94,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C94" s="2">
         <v>1571305865</v>
       </c>
-      <c r="C94" t="s">
-        <v>0</v>
-      </c>
       <c r="D94" t="s">
+        <v>0</v>
+      </c>
+      <c r="E94" t="s">
         <v>190</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>191</v>
       </c>
-      <c r="F94" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G94" t="s">
-        <v>3</v>
+      <c r="G94" s="1">
+        <v>46247</v>
       </c>
       <c r="H94" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I94" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J94" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K94" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L94" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B95)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B95" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C95)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B95" t="str">
+        <f>IF(A95="Ada",IF(IFERROR(VLOOKUP(C95,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C95,Sheet2!A:C,3,FALSE),""),VLOOKUP(C95,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C95" s="2">
         <v>1571305916</v>
       </c>
-      <c r="C95" t="s">
-        <v>0</v>
-      </c>
       <c r="D95" t="s">
+        <v>0</v>
+      </c>
+      <c r="E95" t="s">
         <v>192</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>193</v>
       </c>
-      <c r="F95" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G95" t="s">
-        <v>3</v>
+      <c r="G95" s="1">
+        <v>46247</v>
       </c>
       <c r="H95" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I95" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J95" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K95" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L95" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B96)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B96" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C96)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B96" t="str">
+        <f>IF(A96="Ada",IF(IFERROR(VLOOKUP(C96,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C96,Sheet2!A:C,3,FALSE),""),VLOOKUP(C96,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C96" s="2">
         <v>1571305984</v>
       </c>
-      <c r="C96" t="s">
-        <v>0</v>
-      </c>
       <c r="D96" t="s">
+        <v>0</v>
+      </c>
+      <c r="E96" t="s">
         <v>194</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>195</v>
       </c>
-      <c r="F96" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G96" t="s">
-        <v>3</v>
+      <c r="G96" s="1">
+        <v>46247</v>
       </c>
       <c r="H96" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I96" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J96" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K96" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L96" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B97)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C97)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" t="str">
+        <f>IF(A97="Ada",IF(IFERROR(VLOOKUP(C97,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C97,Sheet2!A:C,3,FALSE),""),VLOOKUP(C97,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>rais nurwahyudin</v>
+      </c>
+      <c r="C97" s="2">
         <v>1571306241</v>
       </c>
-      <c r="C97" t="s">
-        <v>0</v>
-      </c>
       <c r="D97" t="s">
+        <v>0</v>
+      </c>
+      <c r="E97" t="s">
         <v>196</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>197</v>
       </c>
-      <c r="F97" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G97" t="s">
-        <v>3</v>
+      <c r="G97" s="1">
+        <v>46247</v>
       </c>
       <c r="H97" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I97" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J97" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K97" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L97" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B98)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C98)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B98" s="2">
+      <c r="B98" t="str">
+        <f>IF(A98="Ada",IF(IFERROR(VLOOKUP(C98,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C98,Sheet2!A:C,3,FALSE),""),VLOOKUP(C98,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Muhammad Raya Maulana, S.T</v>
+      </c>
+      <c r="C98" s="2">
         <v>1571306264</v>
       </c>
-      <c r="C98" t="s">
-        <v>0</v>
-      </c>
       <c r="D98" t="s">
+        <v>0</v>
+      </c>
+      <c r="E98" t="s">
         <v>198</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>199</v>
       </c>
-      <c r="F98" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G98" t="s">
-        <v>3</v>
+      <c r="G98" s="1">
+        <v>46247</v>
       </c>
       <c r="H98" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I98" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J98" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K98" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L98" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B99)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B99" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C99)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B99" t="str">
+        <f>IF(A99="Ada",IF(IFERROR(VLOOKUP(C99,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C99,Sheet2!A:C,3,FALSE),""),VLOOKUP(C99,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C99" s="2">
         <v>1571306277</v>
       </c>
-      <c r="C99" t="s">
-        <v>0</v>
-      </c>
       <c r="D99" t="s">
+        <v>0</v>
+      </c>
+      <c r="E99" t="s">
         <v>200</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>201</v>
       </c>
-      <c r="F99" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G99" t="s">
-        <v>3</v>
+      <c r="G99" s="1">
+        <v>46247</v>
       </c>
       <c r="H99" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I99" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J99" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K99" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L99" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B100)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B100" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C100)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B100" t="str">
+        <f>IF(A100="Ada",IF(IFERROR(VLOOKUP(C100,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C100,Sheet2!A:C,3,FALSE),""),VLOOKUP(C100,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C100" s="2">
         <v>1571306279</v>
       </c>
-      <c r="C100" t="s">
-        <v>0</v>
-      </c>
       <c r="D100" t="s">
+        <v>0</v>
+      </c>
+      <c r="E100" t="s">
         <v>144</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>145</v>
       </c>
-      <c r="F100" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G100" t="s">
-        <v>3</v>
+      <c r="G100" s="1">
+        <v>46247</v>
       </c>
       <c r="H100" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I100" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J100" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K100" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L100" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B101)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B101" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C101)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B101" t="str">
+        <f>IF(A101="Ada",IF(IFERROR(VLOOKUP(C101,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C101,Sheet2!A:C,3,FALSE),""),VLOOKUP(C101,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C101" s="2">
         <v>1571306608</v>
       </c>
-      <c r="C101" t="s">
-        <v>0</v>
-      </c>
       <c r="D101" t="s">
+        <v>0</v>
+      </c>
+      <c r="E101" t="s">
         <v>202</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>203</v>
       </c>
-      <c r="F101" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G101" t="s">
-        <v>3</v>
+      <c r="G101" s="1">
+        <v>46247</v>
       </c>
       <c r="H101" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I101" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J101" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K101" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L101" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B102)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B102" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C102)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B102" t="str">
+        <f>IF(A102="Ada",IF(IFERROR(VLOOKUP(C102,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C102,Sheet2!A:C,3,FALSE),""),VLOOKUP(C102,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C102" s="2">
         <v>1571306612</v>
       </c>
-      <c r="C102" t="s">
-        <v>0</v>
-      </c>
       <c r="D102" t="s">
+        <v>0</v>
+      </c>
+      <c r="E102" t="s">
         <v>204</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>205</v>
       </c>
-      <c r="F102" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G102" t="s">
-        <v>3</v>
+      <c r="G102" s="1">
+        <v>46247</v>
       </c>
       <c r="H102" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I102" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J102" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K102" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L102" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B103)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B103" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C103)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B103" t="str">
+        <f>IF(A103="Ada",IF(IFERROR(VLOOKUP(C103,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C103,Sheet2!A:C,3,FALSE),""),VLOOKUP(C103,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C103" s="2">
         <v>1571306624</v>
       </c>
-      <c r="C103" t="s">
-        <v>0</v>
-      </c>
       <c r="D103" t="s">
+        <v>0</v>
+      </c>
+      <c r="E103" t="s">
         <v>206</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>207</v>
       </c>
-      <c r="F103" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G103" t="s">
-        <v>3</v>
+      <c r="G103" s="1">
+        <v>46247</v>
       </c>
       <c r="H103" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I103" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J103" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K103" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L103" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B104)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B104" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C104)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B104" t="str">
+        <f>IF(A104="Ada",IF(IFERROR(VLOOKUP(C104,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C104,Sheet2!A:C,3,FALSE),""),VLOOKUP(C104,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C104" s="2">
         <v>1571307032</v>
       </c>
-      <c r="C104" t="s">
-        <v>0</v>
-      </c>
       <c r="D104" t="s">
+        <v>0</v>
+      </c>
+      <c r="E104" t="s">
         <v>208</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>209</v>
       </c>
-      <c r="F104" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G104" t="s">
-        <v>3</v>
+      <c r="G104" s="1">
+        <v>46247</v>
       </c>
       <c r="H104" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I104" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J104" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K104" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L104" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B105)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B105" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C105)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B105" t="str">
+        <f>IF(A105="Ada",IF(IFERROR(VLOOKUP(C105,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C105,Sheet2!A:C,3,FALSE),""),VLOOKUP(C105,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C105" s="2">
         <v>1571307035</v>
       </c>
-      <c r="C105" t="s">
-        <v>0</v>
-      </c>
       <c r="D105" t="s">
+        <v>0</v>
+      </c>
+      <c r="E105" t="s">
         <v>210</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>211</v>
       </c>
-      <c r="F105" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G105" t="s">
-        <v>3</v>
+      <c r="G105" s="1">
+        <v>46247</v>
       </c>
       <c r="H105" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I105" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J105" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K105" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L105" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B106)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B106" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C106)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B106" t="str">
+        <f>IF(A106="Ada",IF(IFERROR(VLOOKUP(C106,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C106,Sheet2!A:C,3,FALSE),""),VLOOKUP(C106,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C106" s="2">
         <v>1571307129</v>
       </c>
-      <c r="C106" t="s">
-        <v>0</v>
-      </c>
       <c r="D106" t="s">
+        <v>0</v>
+      </c>
+      <c r="E106" t="s">
         <v>212</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>213</v>
       </c>
-      <c r="F106" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G106" t="s">
-        <v>3</v>
+      <c r="G106" s="1">
+        <v>46247</v>
       </c>
       <c r="H106" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J106" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K106" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L106" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B107)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C107)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B107" s="2">
+      <c r="B107" t="str">
+        <f>IF(A107="Ada",IF(IFERROR(VLOOKUP(C107,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C107,Sheet2!A:C,3,FALSE),""),VLOOKUP(C107,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Putri Taqwa Prasetyaningrum</v>
+      </c>
+      <c r="C107" s="2">
         <v>1571307383</v>
       </c>
-      <c r="C107" t="s">
-        <v>0</v>
-      </c>
       <c r="D107" t="s">
+        <v>0</v>
+      </c>
+      <c r="E107" t="s">
         <v>214</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>215</v>
       </c>
-      <c r="F107" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G107" t="s">
-        <v>3</v>
+      <c r="G107" s="1">
+        <v>46247</v>
       </c>
       <c r="H107" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I107" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J107" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K107" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L107" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B108)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B108" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C108)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B108" t="str">
+        <f>IF(A108="Ada",IF(IFERROR(VLOOKUP(C108,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C108,Sheet2!A:C,3,FALSE),""),VLOOKUP(C108,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C108" s="2">
         <v>1571307415</v>
       </c>
-      <c r="C108" t="s">
-        <v>0</v>
-      </c>
       <c r="D108" t="s">
+        <v>0</v>
+      </c>
+      <c r="E108" t="s">
         <v>216</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>217</v>
       </c>
-      <c r="F108" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G108" t="s">
-        <v>3</v>
+      <c r="G108" s="1">
+        <v>46247</v>
       </c>
       <c r="H108" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I108" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J108" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K108" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L108" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B109)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C109)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B109" s="2">
+      <c r="B109" t="str">
+        <f>IF(A109="Ada",IF(IFERROR(VLOOKUP(C109,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C109,Sheet2!A:C,3,FALSE),""),VLOOKUP(C109,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Fadli Sirait, S.Si, M.T, Ph.D</v>
+      </c>
+      <c r="C109" s="2">
         <v>1571307433</v>
       </c>
-      <c r="C109" t="s">
-        <v>0</v>
-      </c>
       <c r="D109" t="s">
+        <v>0</v>
+      </c>
+      <c r="E109" t="s">
         <v>218</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>219</v>
       </c>
-      <c r="F109" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G109" t="s">
-        <v>3</v>
+      <c r="G109" s="1">
+        <v>46247</v>
       </c>
       <c r="H109" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I109" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J109" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K109" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L109" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B110)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B110" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C110)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B110" t="str">
+        <f>IF(A110="Ada",IF(IFERROR(VLOOKUP(C110,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C110,Sheet2!A:C,3,FALSE),""),VLOOKUP(C110,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C110" s="2">
         <v>1571307467</v>
       </c>
-      <c r="C110" t="s">
-        <v>0</v>
-      </c>
       <c r="D110" t="s">
+        <v>0</v>
+      </c>
+      <c r="E110" t="s">
         <v>220</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>221</v>
       </c>
-      <c r="F110" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G110" t="s">
-        <v>3</v>
+      <c r="G110" s="1">
+        <v>46247</v>
       </c>
       <c r="H110" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I110" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J110" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K110" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L110" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B111)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B111" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C111)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B111" t="str">
+        <f>IF(A111="Ada",IF(IFERROR(VLOOKUP(C111,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C111,Sheet2!A:C,3,FALSE),""),VLOOKUP(C111,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C111" s="2">
         <v>1571307511</v>
       </c>
-      <c r="C111" t="s">
-        <v>0</v>
-      </c>
       <c r="D111" t="s">
+        <v>0</v>
+      </c>
+      <c r="E111" t="s">
         <v>222</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>223</v>
       </c>
-      <c r="F111" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G111" t="s">
-        <v>3</v>
+      <c r="G111" s="1">
+        <v>46247</v>
       </c>
       <c r="H111" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I111" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J111" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K111" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L111" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B112)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B112" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C112)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B112" t="str">
+        <f>IF(A112="Ada",IF(IFERROR(VLOOKUP(C112,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C112,Sheet2!A:C,3,FALSE),""),VLOOKUP(C112,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C112" s="2">
         <v>1571307533</v>
       </c>
-      <c r="C112" t="s">
-        <v>0</v>
-      </c>
       <c r="D112" t="s">
+        <v>0</v>
+      </c>
+      <c r="E112" t="s">
         <v>224</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>225</v>
       </c>
-      <c r="F112" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G112" t="s">
-        <v>3</v>
+      <c r="G112" s="1">
+        <v>46247</v>
       </c>
       <c r="H112" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I112" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J112" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K112" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L112" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B113)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B113" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C113)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B113" t="str">
+        <f>IF(A113="Ada",IF(IFERROR(VLOOKUP(C113,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C113,Sheet2!A:C,3,FALSE),""),VLOOKUP(C113,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C113" s="2">
         <v>1571307597</v>
       </c>
-      <c r="C113" t="s">
-        <v>0</v>
-      </c>
       <c r="D113" t="s">
+        <v>0</v>
+      </c>
+      <c r="E113" t="s">
         <v>226</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>227</v>
       </c>
-      <c r="F113" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G113" t="s">
-        <v>3</v>
+      <c r="G113" s="1">
+        <v>46247</v>
       </c>
       <c r="H113" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I113" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J113" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K113" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L113" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B114)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B114" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C114)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B114" t="str">
+        <f>IF(A114="Ada",IF(IFERROR(VLOOKUP(C114,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C114,Sheet2!A:C,3,FALSE),""),VLOOKUP(C114,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C114" s="2">
         <v>1571307615</v>
       </c>
-      <c r="C114" t="s">
-        <v>0</v>
-      </c>
       <c r="D114" t="s">
+        <v>0</v>
+      </c>
+      <c r="E114" t="s">
         <v>228</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>229</v>
       </c>
-      <c r="F114" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G114" t="s">
-        <v>3</v>
+      <c r="G114" s="1">
+        <v>46247</v>
       </c>
       <c r="H114" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I114" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J114" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K114" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L114" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B115)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C115)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B115" s="2">
+      <c r="B115" t="str">
+        <f>IF(A115="Ada",IF(IFERROR(VLOOKUP(C115,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C115,Sheet2!A:C,3,FALSE),""),VLOOKUP(C115,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Lintang Deni Laksana</v>
+      </c>
+      <c r="C115" s="2">
         <v>1571307622</v>
       </c>
-      <c r="C115" t="s">
-        <v>0</v>
-      </c>
       <c r="D115" t="s">
+        <v>0</v>
+      </c>
+      <c r="E115" t="s">
         <v>230</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>231</v>
       </c>
-      <c r="F115" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G115" t="s">
-        <v>3</v>
+      <c r="G115" s="1">
+        <v>46247</v>
       </c>
       <c r="H115" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I115" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J115" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K115" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L115" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B116)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B116" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C116)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B116" t="str">
+        <f>IF(A116="Ada",IF(IFERROR(VLOOKUP(C116,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C116,Sheet2!A:C,3,FALSE),""),VLOOKUP(C116,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C116" s="2">
         <v>1571307624</v>
       </c>
-      <c r="C116" t="s">
-        <v>0</v>
-      </c>
       <c r="D116" t="s">
+        <v>0</v>
+      </c>
+      <c r="E116" t="s">
         <v>232</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>233</v>
       </c>
-      <c r="F116" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G116" t="s">
-        <v>3</v>
+      <c r="G116" s="1">
+        <v>46247</v>
       </c>
       <c r="H116" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I116" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J116" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K116" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L116" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B117)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B117" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C117)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B117" t="str">
+        <f>IF(A117="Ada",IF(IFERROR(VLOOKUP(C117,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C117,Sheet2!A:C,3,FALSE),""),VLOOKUP(C117,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C117" s="2">
         <v>1571307635</v>
       </c>
-      <c r="C117" t="s">
-        <v>0</v>
-      </c>
       <c r="D117" t="s">
+        <v>0</v>
+      </c>
+      <c r="E117" t="s">
         <v>234</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>235</v>
       </c>
-      <c r="F117" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G117" t="s">
-        <v>3</v>
+      <c r="G117" s="1">
+        <v>46247</v>
       </c>
       <c r="H117" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I117" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J117" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K117" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L117" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B118)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B118" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C118)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B118" t="str">
+        <f>IF(A118="Ada",IF(IFERROR(VLOOKUP(C118,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C118,Sheet2!A:C,3,FALSE),""),VLOOKUP(C118,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C118" s="2">
         <v>1571307652</v>
       </c>
-      <c r="C118" t="s">
-        <v>0</v>
-      </c>
       <c r="D118" t="s">
+        <v>0</v>
+      </c>
+      <c r="E118" t="s">
         <v>236</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>237</v>
       </c>
-      <c r="F118" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G118" t="s">
-        <v>3</v>
+      <c r="G118" s="1">
+        <v>46247</v>
       </c>
       <c r="H118" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I118" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J118" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K118" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L118" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B119)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B119" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C119)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B119" t="str">
+        <f>IF(A119="Ada",IF(IFERROR(VLOOKUP(C119,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C119,Sheet2!A:C,3,FALSE),""),VLOOKUP(C119,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C119" s="2">
         <v>1571307660</v>
       </c>
-      <c r="C119" t="s">
-        <v>0</v>
-      </c>
       <c r="D119" t="s">
+        <v>0</v>
+      </c>
+      <c r="E119" t="s">
         <v>238</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>239</v>
       </c>
-      <c r="F119" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G119" t="s">
-        <v>3</v>
+      <c r="G119" s="1">
+        <v>46247</v>
       </c>
       <c r="H119" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I119" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J119" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K119" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L119" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B120)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C120)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B120" s="2">
+      <c r="B120" t="str">
+        <f>IF(A120="Ada",IF(IFERROR(VLOOKUP(C120,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C120,Sheet2!A:C,3,FALSE),""),VLOOKUP(C120,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Mohammad Noer Dafiq</v>
+      </c>
+      <c r="C120" s="2">
         <v>1571307671</v>
       </c>
-      <c r="C120" t="s">
-        <v>0</v>
-      </c>
       <c r="D120" t="s">
+        <v>0</v>
+      </c>
+      <c r="E120" t="s">
         <v>240</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>241</v>
       </c>
-      <c r="F120" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G120" t="s">
-        <v>3</v>
+      <c r="G120" s="1">
+        <v>46247</v>
       </c>
       <c r="H120" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I120" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J120" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K120" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L120" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B121)&gt;0,"Ada","Tidak Ada")</f>
+        <f>IF(COUNTIF(Sheet2!A:A,C121)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B121" s="2">
+      <c r="B121" t="str">
+        <f>IF(A121="Ada",IF(IFERROR(VLOOKUP(C121,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C121,Sheet2!A:C,3,FALSE),""),VLOOKUP(C121,Sheet2!A:C,2,FALSE)),"")</f>
+        <v>Nurwahid Rahman</v>
+      </c>
+      <c r="C121" s="2">
         <v>1571307676</v>
       </c>
-      <c r="C121" t="s">
-        <v>0</v>
-      </c>
       <c r="D121" t="s">
+        <v>0</v>
+      </c>
+      <c r="E121" t="s">
         <v>242</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
         <v>243</v>
       </c>
-      <c r="F121" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G121" t="s">
-        <v>3</v>
+      <c r="G121" s="1">
+        <v>46247</v>
       </c>
       <c r="H121" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I121" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J121" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K121" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L121" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B122)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B122" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C122)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B122" t="str">
+        <f>IF(A122="Ada",IF(IFERROR(VLOOKUP(C122,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C122,Sheet2!A:C,3,FALSE),""),VLOOKUP(C122,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C122" s="2">
         <v>1571307682</v>
       </c>
-      <c r="C122" t="s">
-        <v>0</v>
-      </c>
       <c r="D122" t="s">
+        <v>0</v>
+      </c>
+      <c r="E122" t="s">
         <v>244</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>245</v>
       </c>
-      <c r="F122" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G122" t="s">
-        <v>3</v>
+      <c r="G122" s="1">
+        <v>46247</v>
       </c>
       <c r="H122" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I122" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J122" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K122" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L122" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B123)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B123" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C123)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B123" t="str">
+        <f>IF(A123="Ada",IF(IFERROR(VLOOKUP(C123,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C123,Sheet2!A:C,3,FALSE),""),VLOOKUP(C123,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C123" s="2">
         <v>1571307703</v>
       </c>
-      <c r="C123" t="s">
-        <v>0</v>
-      </c>
       <c r="D123" t="s">
+        <v>0</v>
+      </c>
+      <c r="E123" t="s">
         <v>246</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>247</v>
       </c>
-      <c r="F123" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G123" t="s">
-        <v>3</v>
+      <c r="G123" s="1">
+        <v>46247</v>
       </c>
       <c r="H123" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I123" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J123" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K123" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L123" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B124)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B124" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C124)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B124" t="str">
+        <f>IF(A124="Ada",IF(IFERROR(VLOOKUP(C124,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C124,Sheet2!A:C,3,FALSE),""),VLOOKUP(C124,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C124" s="2">
         <v>1571308724</v>
       </c>
-      <c r="C124" t="s">
-        <v>0</v>
-      </c>
       <c r="D124" t="s">
+        <v>0</v>
+      </c>
+      <c r="E124" t="s">
         <v>248</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>249</v>
       </c>
-      <c r="F124" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G124" t="s">
-        <v>3</v>
+      <c r="G124" s="1">
+        <v>46247</v>
       </c>
       <c r="H124" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I124" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J124" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K124" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L124" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B125)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B125" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C125)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B125" t="str">
+        <f>IF(A125="Ada",IF(IFERROR(VLOOKUP(C125,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C125,Sheet2!A:C,3,FALSE),""),VLOOKUP(C125,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C125" s="2">
         <v>1571308850</v>
       </c>
-      <c r="C125" t="s">
-        <v>0</v>
-      </c>
       <c r="D125" t="s">
+        <v>0</v>
+      </c>
+      <c r="E125" t="s">
         <v>250</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>251</v>
       </c>
-      <c r="F125" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G125" t="s">
-        <v>3</v>
+      <c r="G125" s="1">
+        <v>46247</v>
       </c>
       <c r="H125" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I125" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J125" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K125" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L125" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B126)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B126" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C126)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B126" t="str">
+        <f>IF(A126="Ada",IF(IFERROR(VLOOKUP(C126,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C126,Sheet2!A:C,3,FALSE),""),VLOOKUP(C126,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C126" s="2">
         <v>1571309340</v>
       </c>
-      <c r="C126" t="s">
-        <v>0</v>
-      </c>
       <c r="D126" t="s">
+        <v>0</v>
+      </c>
+      <c r="E126" t="s">
         <v>252</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>253</v>
       </c>
-      <c r="F126" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G126" t="s">
-        <v>3</v>
+      <c r="G126" s="1">
+        <v>46247</v>
       </c>
       <c r="H126" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I126" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J126" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K126" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="L126" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="str">
-        <f>IF(COUNTIF(Sheet2!A:A,B127)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B127" s="2">
+        <f>IF(COUNTIF(Sheet2!A:A,C127)&gt;0,"Ada","Tidak Ada")</f>
+        <v>Tidak Ada</v>
+      </c>
+      <c r="B127" t="str">
+        <f>IF(A127="Ada",IF(IFERROR(VLOOKUP(C127,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C127,Sheet2!A:C,3,FALSE),""),VLOOKUP(C127,Sheet2!A:C,2,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="C127" s="2">
         <v>1571310439</v>
       </c>
-      <c r="C127" t="s">
-        <v>0</v>
-      </c>
       <c r="D127" t="s">
+        <v>0</v>
+      </c>
+      <c r="E127" t="s">
         <v>254</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>255</v>
       </c>
-      <c r="F127" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G127" t="s">
-        <v>3</v>
+      <c r="G127" s="1">
+        <v>46247</v>
       </c>
       <c r="H127" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I127" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J127" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K127" t="s">
+        <v>6</v>
+      </c>
+      <c r="L127" t="s">
         <v>7</v>
       </c>
     </row>
@@ -5780,220 +6460,434 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{425A0240-4B53-4571-9694-7E2E7C87F1EF}">
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="60.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1571279780</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1571267967</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1571294926</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1571306264</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1571290818</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1571307622</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1571298976</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1571305337</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1571290388</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1571291668</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1571303126</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1571282959</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1571300706</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>264</v>
+      </c>
+      <c r="C13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1571291423</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1571307383</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C15" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1571297897</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>266</v>
+      </c>
+      <c r="C16" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1571305741</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1571298558</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1571298209</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1571306241</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1571290388</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1571298045</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1571296305</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>268</v>
+      </c>
+      <c r="C23" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1571298458</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>269</v>
+      </c>
+      <c r="C24" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1571291935</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1571305122</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>270</v>
+      </c>
+      <c r="C26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1571305360</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C27" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1571291877</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>272</v>
+      </c>
+      <c r="C28" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1571305354</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>273</v>
+      </c>
+      <c r="C29" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1571305199</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>274</v>
+      </c>
+      <c r="C30" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1571304164</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C31" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1571307676</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>276</v>
+      </c>
+      <c r="C32" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1571291638</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C33" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1571307671</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>277</v>
+      </c>
+      <c r="C34" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1571289829</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C35" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1571291625</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>278</v>
+      </c>
+      <c r="C36" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1571305316</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C37" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1571307433</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C38" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>2524612</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>279</v>
+      </c>
+      <c r="C39" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1571300264</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>280</v>
+      </c>
+      <c r="C40" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1571304164</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>275</v>
+      </c>
+      <c r="C41" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1571297897</v>
+      </c>
+      <c r="B42" t="s">
+        <v>266</v>
+      </c>
+      <c r="C42" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>1571304167</v>
+      </c>
+      <c r="B43" t="s">
+        <v>281</v>
+      </c>
+      <c r="C43" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/Cek Validasi.xlsx
+++ b/Cek Validasi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\icvee\ICVEE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D703EF-BCCD-4C4B-8899-7720680DF220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CFBF2C-3F93-4C40-9C6F-8ED85877AF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9BCEFB9A-EF35-43F1-AD2F-79243D21B5CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9BCEFB9A-EF35-43F1-AD2F-79243D21B5CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="320">
   <si>
     <t>accepted</t>
   </si>
@@ -985,6 +985,21 @@
   </si>
   <si>
     <t>Abdullah Billman</t>
+  </si>
+  <si>
+    <t>Yan Watequlis Syaifudin</t>
+  </si>
+  <si>
+    <t>Osmalina Nur Rahma, S.T., M.Si.</t>
+  </si>
+  <si>
+    <t>I Gusti bagus Wiraditya</t>
+  </si>
+  <si>
+    <t>Prof. Ir. Yan Watequlis Syaifudin, ST., M.MT., Ph.D.</t>
+  </si>
+  <si>
+    <t>Rifqi Abdillah</t>
   </si>
 </sst>
 </file>
@@ -1378,9 +1393,8 @@
       <c r="A1" t="s">
         <v>257</v>
       </c>
-      <c r="B1">
-        <f>IF(A1="Ada", 1, 0)</f>
-        <v>1</v>
+      <c r="B1" t="s">
+        <v>319</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>256</v>
@@ -1456,11 +1470,11 @@
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C3)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B3" t="str">
         <f>IF(A3="Ada",IF(IFERROR(VLOOKUP(C3,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C3,Sheet2!A:C,3,FALSE),""),VLOOKUP(C3,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Dr. I Nyoman Kusuma Wardana</v>
       </c>
       <c r="C3" s="2">
         <v>1571267469</v>
@@ -1496,11 +1510,11 @@
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C4)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B4" t="str">
         <f>IF(A4="Ada",IF(IFERROR(VLOOKUP(C4,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C4,Sheet2!A:C,3,FALSE),""),VLOOKUP(C4,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Athif Fadheel Atharahman</v>
       </c>
       <c r="C4" s="2">
         <v>1571267484</v>
@@ -1540,7 +1554,7 @@
       </c>
       <c r="B5" t="str">
         <f>IF(A5="Ada",IF(IFERROR(VLOOKUP(C5,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C5,Sheet2!A:C,3,FALSE),""),VLOOKUP(C5,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Athif Fadheel Atharahman</v>
+        <v>Muhammad Andika Fadilla, S.Kom</v>
       </c>
       <c r="C5" s="2">
         <v>1571267967</v>
@@ -1576,11 +1590,11 @@
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C6)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B6" t="str">
         <f>IF(A6="Ada",IF(IFERROR(VLOOKUP(C6,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C6,Sheet2!A:C,3,FALSE),""),VLOOKUP(C6,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Muhammad Raya Maulana, S.T</v>
       </c>
       <c r="C6" s="2">
         <v>1571268176</v>
@@ -1660,7 +1674,7 @@
       </c>
       <c r="B8" t="str">
         <f>IF(A8="Ada",IF(IFERROR(VLOOKUP(C8,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C8,Sheet2!A:C,3,FALSE),""),VLOOKUP(C8,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Dr. I Nyoman Kusuma Wardana</v>
+        <v>Dr. Hendy Briantoro</v>
       </c>
       <c r="C8" s="2">
         <v>1571279780</v>
@@ -1696,11 +1710,11 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C9)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B9" t="str">
         <f>IF(A9="Ada",IF(IFERROR(VLOOKUP(C9,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C9,Sheet2!A:C,3,FALSE),""),VLOOKUP(C9,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Lintang Deni Laksana</v>
       </c>
       <c r="C9" s="2">
         <v>1571280074</v>
@@ -1776,11 +1790,11 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C11)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B11" t="str">
         <f>IF(A11="Ada",IF(IFERROR(VLOOKUP(C11,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C11,Sheet2!A:C,3,FALSE),""),VLOOKUP(C11,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Mr. Fajar Romadhan</v>
       </c>
       <c r="C11" s="2">
         <v>1571281021</v>
@@ -1816,11 +1830,11 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C12)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B12" t="str">
         <f>IF(A12="Ada",IF(IFERROR(VLOOKUP(C12,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C12,Sheet2!A:C,3,FALSE),""),VLOOKUP(C12,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Mrs. Alya Esa Mentari</v>
       </c>
       <c r="C12" s="2">
         <v>1571281084</v>
@@ -1860,7 +1874,7 @@
       </c>
       <c r="B13" t="str">
         <f>IF(A13="Ada",IF(IFERROR(VLOOKUP(C13,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C13,Sheet2!A:C,3,FALSE),""),VLOOKUP(C13,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Afandi Sahputra, S.T., M.T.</v>
+        <v>Nathanael Sitanggang; Putri Lynna A Luthan</v>
       </c>
       <c r="C13" s="2">
         <v>1571282959</v>
@@ -1936,11 +1950,11 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C15)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B15" t="str">
         <f>IF(A15="Ada",IF(IFERROR(VLOOKUP(C15,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C15,Sheet2!A:C,3,FALSE),""),VLOOKUP(C15,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Annisya Diaz Chandradewi, Dwi Dya Nindasari</v>
       </c>
       <c r="C15" s="2">
         <v>1571286979</v>
@@ -2020,7 +2034,7 @@
       </c>
       <c r="B17" t="str">
         <f>IF(A17="Ada",IF(IFERROR(VLOOKUP(C17,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C17,Sheet2!A:C,3,FALSE),""),VLOOKUP(C17,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Eko Puji Laksono, S.Kom.,M.Kom</v>
+        <v>Kurnia Chairunnisa</v>
       </c>
       <c r="C17" s="2">
         <v>1571289829</v>
@@ -2060,7 +2074,7 @@
       </c>
       <c r="B18" t="str">
         <f>IF(A18="Ada",IF(IFERROR(VLOOKUP(C18,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C18,Sheet2!A:C,3,FALSE),""),VLOOKUP(C18,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Nathanael Sitanggang; Putri Lynna A Luthan</v>
+        <v>Afandi Sahputra, S.T., M.T.</v>
       </c>
       <c r="C18" s="2">
         <v>1571290388</v>
@@ -2140,7 +2154,7 @@
       </c>
       <c r="B20" t="str">
         <f>IF(A20="Ada",IF(IFERROR(VLOOKUP(C20,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C20,Sheet2!A:C,3,FALSE),""),VLOOKUP(C20,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Dr. Hendy Briantoro</v>
+        <v>Albertus Andika Tri Anggoro</v>
       </c>
       <c r="C20" s="2">
         <v>1571290818</v>
@@ -2256,11 +2270,11 @@
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C23)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B23" t="str">
         <f>IF(A23="Ada",IF(IFERROR(VLOOKUP(C23,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C23,Sheet2!A:C,3,FALSE),""),VLOOKUP(C23,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Hamid Rahman, M.Kom.</v>
       </c>
       <c r="C23" s="2">
         <v>1571291272</v>
@@ -2300,7 +2314,7 @@
       </c>
       <c r="B24" t="str">
         <f>IF(A24="Ada",IF(IFERROR(VLOOKUP(C24,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C24,Sheet2!A:C,3,FALSE),""),VLOOKUP(C24,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Hamid Rahman, M.Kom.</v>
+        <v>Putri Taqwa Prasetyaningrum</v>
       </c>
       <c r="C24" s="2">
         <v>1571291423</v>
@@ -2340,7 +2354,7 @@
       </c>
       <c r="B25" t="str">
         <f>IF(A25="Ada",IF(IFERROR(VLOOKUP(C25,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C25,Sheet2!A:C,3,FALSE),""),VLOOKUP(C25,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>DAVE SHANNA MARIE E. GIGAWIN &amp; JOHN PAUL L. ULLEGUE</v>
+        <v>Nanditya Vianti Putri</v>
       </c>
       <c r="C25" s="2">
         <v>1571291625</v>
@@ -2380,7 +2394,7 @@
       </c>
       <c r="B26" t="str">
         <f>IF(A26="Ada",IF(IFERROR(VLOOKUP(C26,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C26,Sheet2!A:C,3,FALSE),""),VLOOKUP(C26,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Eric Julianto</v>
+        <v>: Juris Vassa Ivandro, S.Kom</v>
       </c>
       <c r="C26" s="2">
         <v>1571291638</v>
@@ -2420,7 +2434,7 @@
       </c>
       <c r="B27" t="str">
         <f>IF(A27="Ada",IF(IFERROR(VLOOKUP(C27,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C27,Sheet2!A:C,3,FALSE),""),VLOOKUP(C27,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Annisya Diaz Chandradewi, Dwi Dya Nindasari</v>
+        <v>Anisa Dzulkarnain, S.Kom., M.Kom.</v>
       </c>
       <c r="C27" s="2">
         <v>1571291668</v>
@@ -2580,7 +2594,7 @@
       </c>
       <c r="B31" t="str">
         <f>IF(A31="Ada",IF(IFERROR(VLOOKUP(C31,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C31,Sheet2!A:C,3,FALSE),""),VLOOKUP(C31,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Veldin A. Talorete Jr.</v>
+        <v>SUGITO, S.Kom</v>
       </c>
       <c r="C31" s="2">
         <v>1571291877</v>
@@ -2660,7 +2674,7 @@
       </c>
       <c r="B33" t="str">
         <f>IF(A33="Ada",IF(IFERROR(VLOOKUP(C33,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C33,Sheet2!A:C,3,FALSE),""),VLOOKUP(C33,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Fauziyah Wafa'Abdillah, S.Tr.T.</v>
+        <v>rais nurwahyudin</v>
       </c>
       <c r="C33" s="2">
         <v>1571291935</v>
@@ -2936,11 +2950,11 @@
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C40)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B40" t="str">
         <f>IF(A40="Ada",IF(IFERROR(VLOOKUP(C40,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C40,Sheet2!A:C,3,FALSE),""),VLOOKUP(C40,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Prof. Nathanael Sitanggang; Prof. Putri Lynna A. Luthan</v>
       </c>
       <c r="C40" s="2">
         <v>1571292356</v>
@@ -3056,11 +3070,11 @@
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C43)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B43" t="str">
         <f>IF(A43="Ada",IF(IFERROR(VLOOKUP(C43,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C43,Sheet2!A:C,3,FALSE),""),VLOOKUP(C43,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Sugeng Hari Wibowo</v>
       </c>
       <c r="C43" s="2">
         <v>1571292417</v>
@@ -3100,7 +3114,7 @@
       </c>
       <c r="B44" t="str">
         <f>IF(A44="Ada",IF(IFERROR(VLOOKUP(C44,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C44,Sheet2!A:C,3,FALSE),""),VLOOKUP(C44,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Muhammad Andika Fadilla, S.Kom</v>
+        <v>Beny Prasetyo</v>
       </c>
       <c r="C44" s="2">
         <v>1571294926</v>
@@ -3176,11 +3190,11 @@
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C46)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B46" t="str">
         <f>IF(A46="Ada",IF(IFERROR(VLOOKUP(C46,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C46,Sheet2!A:C,3,FALSE),""),VLOOKUP(C46,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Maskur</v>
       </c>
       <c r="C46" s="2">
         <v>1571295713</v>
@@ -3220,7 +3234,7 @@
       </c>
       <c r="B47" t="str">
         <f>IF(A47="Ada",IF(IFERROR(VLOOKUP(C47,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C47,Sheet2!A:C,3,FALSE),""),VLOOKUP(C47,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Beny Prasetyo</v>
+        <v>Fauziyah Wafa'Abdillah, S.Tr.T.</v>
       </c>
       <c r="C47" s="2">
         <v>1571296305</v>
@@ -3380,7 +3394,7 @@
       </c>
       <c r="B51" t="str">
         <f>IF(A51="Ada",IF(IFERROR(VLOOKUP(C51,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C51,Sheet2!A:C,3,FALSE),""),VLOOKUP(C51,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Nanditya Vianti Putri</v>
+        <v>Putri Christianti Harefa</v>
       </c>
       <c r="C51" s="2">
         <v>1571297897</v>
@@ -3416,11 +3430,11 @@
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C52)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B52" t="str">
         <f>IF(A52="Ada",IF(IFERROR(VLOOKUP(C52,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C52,Sheet2!A:C,3,FALSE),""),VLOOKUP(C52,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Stephanie Debora Assa</v>
       </c>
       <c r="C52" s="2">
         <v>1571298038</v>
@@ -3460,7 +3474,7 @@
       </c>
       <c r="B53" t="str">
         <f>IF(A53="Ada",IF(IFERROR(VLOOKUP(C53,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C53,Sheet2!A:C,3,FALSE),""),VLOOKUP(C53,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Sugeng Hari Wibowo</v>
+        <v>Veldin A. Talorete Jr.</v>
       </c>
       <c r="C53" s="2">
         <v>1571298045</v>
@@ -3500,7 +3514,7 @@
       </c>
       <c r="B54" t="str">
         <f>IF(A54="Ada",IF(IFERROR(VLOOKUP(C54,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C54,Sheet2!A:C,3,FALSE),""),VLOOKUP(C54,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>SUGITO, S.Kom</v>
+        <v>Ramadhani Vanva Fauzia</v>
       </c>
       <c r="C54" s="2">
         <v>1571298209</v>
@@ -3576,11 +3590,11 @@
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C56)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B56" t="str">
         <f>IF(A56="Ada",IF(IFERROR(VLOOKUP(C56,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C56,Sheet2!A:C,3,FALSE),""),VLOOKUP(C56,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Mifta Nur Farid</v>
       </c>
       <c r="C56" s="2">
         <v>1571298278</v>
@@ -3700,7 +3714,7 @@
       </c>
       <c r="B59" t="str">
         <f>IF(A59="Ada",IF(IFERROR(VLOOKUP(C59,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C59,Sheet2!A:C,3,FALSE),""),VLOOKUP(C59,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Maskur</v>
+        <v>Aditya Sheva Pratama</v>
       </c>
       <c r="C59" s="2">
         <v>1571298458</v>
@@ -3860,7 +3874,7 @@
       </c>
       <c r="B63" t="str">
         <f>IF(A63="Ada",IF(IFERROR(VLOOKUP(C63,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C63,Sheet2!A:C,3,FALSE),""),VLOOKUP(C63,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Anisa Dzulkarnain, S.Kom., M.Kom.</v>
+        <v>Nurwahid Rahman</v>
       </c>
       <c r="C63" s="2">
         <v>1571298558</v>
@@ -3980,7 +3994,7 @@
       </c>
       <c r="B66" t="str">
         <f>IF(A66="Ada",IF(IFERROR(VLOOKUP(C66,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C66,Sheet2!A:C,3,FALSE),""),VLOOKUP(C66,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Mr. Fajar Romadhan</v>
+        <v>Eric Julianto</v>
       </c>
       <c r="C66" s="2">
         <v>1571298976</v>
@@ -4060,7 +4074,7 @@
       </c>
       <c r="B68" t="str">
         <f>IF(A68="Ada",IF(IFERROR(VLOOKUP(C68,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C68,Sheet2!A:C,3,FALSE),""),VLOOKUP(C68,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Chandra Restu Pradipto, Aloysius Bernanda Gunawan, Bambang Pratama</v>
+        <v>Mohammad Noer Dafiq</v>
       </c>
       <c r="C68" s="2">
         <v>1571300264</v>
@@ -4096,11 +4110,11 @@
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C69)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B69" t="str">
         <f>IF(A69="Ada",IF(IFERROR(VLOOKUP(C69,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C69,Sheet2!A:C,3,FALSE),""),VLOOKUP(C69,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Eko Puji Laksono, S.Kom.,M.Kom</v>
       </c>
       <c r="C69" s="2">
         <v>1571300636</v>
@@ -4140,7 +4154,7 @@
       </c>
       <c r="B70" t="str">
         <f>IF(A70="Ada",IF(IFERROR(VLOOKUP(C70,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C70,Sheet2!A:C,3,FALSE),""),VLOOKUP(C70,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Albertus Andika Tri Anggoro</v>
+        <v>DAVE SHANNA MARIE E. GIGAWIN &amp; JOHN PAUL L. ULLEGUE</v>
       </c>
       <c r="C70" s="2">
         <v>1571300706</v>
@@ -4176,11 +4190,11 @@
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C71)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B71" t="str">
         <f>IF(A71="Ada",IF(IFERROR(VLOOKUP(C71,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C71,Sheet2!A:C,3,FALSE),""),VLOOKUP(C71,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Hastupara Amurwojakti</v>
       </c>
       <c r="C71" s="2">
         <v>1571301191</v>
@@ -4260,7 +4274,7 @@
       </c>
       <c r="B73" t="str">
         <f>IF(A73="Ada",IF(IFERROR(VLOOKUP(C73,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C73,Sheet2!A:C,3,FALSE),""),VLOOKUP(C73,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Kurnia Chairunnisa</v>
+        <v>Fadli Sirait, S.Si, M.T, Ph.D</v>
       </c>
       <c r="C73" s="2">
         <v>1571303126</v>
@@ -4300,7 +4314,7 @@
       </c>
       <c r="B74" t="str">
         <f>IF(A74="Ada",IF(IFERROR(VLOOKUP(C74,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C74,Sheet2!A:C,3,FALSE),""),VLOOKUP(C74,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Aditya Sheva Pratama</v>
+        <v>-</v>
       </c>
       <c r="C74" s="2">
         <v>1571304164</v>
@@ -4340,7 +4354,7 @@
       </c>
       <c r="B75" t="str">
         <f>IF(A75="Ada",IF(IFERROR(VLOOKUP(C75,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C75,Sheet2!A:C,3,FALSE),""),VLOOKUP(C75,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Muhammad Fahry Ali</v>
+        <v>Chandra Restu Pradipto, Aloysius Bernanda Gunawan, Bambang Pratama</v>
       </c>
       <c r="C75" s="2">
         <v>1571304167</v>
@@ -4496,11 +4510,11 @@
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C79)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B79" t="str">
         <f>IF(A79="Ada",IF(IFERROR(VLOOKUP(C79,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C79,Sheet2!A:C,3,FALSE),""),VLOOKUP(C79,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Aditya Sheva Pratama</v>
       </c>
       <c r="C79" s="2">
         <v>1571304705</v>
@@ -4536,11 +4550,11 @@
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C80)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B80" t="str">
         <f>IF(A80="Ada",IF(IFERROR(VLOOKUP(C80,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C80,Sheet2!A:C,3,FALSE),""),VLOOKUP(C80,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Nanditya Vianti Putri</v>
       </c>
       <c r="C80" s="2">
         <v>1571304827</v>
@@ -4580,7 +4594,7 @@
       </c>
       <c r="B81" t="str">
         <f>IF(A81="Ada",IF(IFERROR(VLOOKUP(C81,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C81,Sheet2!A:C,3,FALSE),""),VLOOKUP(C81,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Putri Christianti Harefa</v>
+        <v>Muhammad Fahry Ali</v>
       </c>
       <c r="C81" s="2">
         <v>1571305122</v>
@@ -4700,7 +4714,7 @@
       </c>
       <c r="B84" t="str">
         <f>IF(A84="Ada",IF(IFERROR(VLOOKUP(C84,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C84,Sheet2!A:C,3,FALSE),""),VLOOKUP(C84,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Mifta Nur Farid</v>
+        <v>Osmalina Nur Rahma, S.T., M.Si.</v>
       </c>
       <c r="C84" s="2">
         <v>1571305199</v>
@@ -4776,11 +4790,11 @@
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C86)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B86" t="str">
         <f>IF(A86="Ada",IF(IFERROR(VLOOKUP(C86,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C86,Sheet2!A:C,3,FALSE),""),VLOOKUP(C86,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>I Gusti bagus Wiraditya</v>
       </c>
       <c r="C86" s="2">
         <v>1571305279</v>
@@ -4820,7 +4834,7 @@
       </c>
       <c r="B87" t="str">
         <f>IF(A87="Ada",IF(IFERROR(VLOOKUP(C87,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C87,Sheet2!A:C,3,FALSE),""),VLOOKUP(C87,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Hastupara Amurwojakti</v>
+        <v>Muhammad Fahry Ali</v>
       </c>
       <c r="C87" s="2">
         <v>1571305316</v>
@@ -4860,7 +4874,7 @@
       </c>
       <c r="B88" t="str">
         <f>IF(A88="Ada",IF(IFERROR(VLOOKUP(C88,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C88,Sheet2!A:C,3,FALSE),""),VLOOKUP(C88,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Mrs. Alya Esa Mentari</v>
+        <v>Yan Watequlis Syaifudin</v>
       </c>
       <c r="C88" s="2">
         <v>1571305337</v>
@@ -4898,9 +4912,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C89)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B89" t="str">
+      <c r="B89">
         <f>IF(A89="Ada",IF(IFERROR(VLOOKUP(C89,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C89,Sheet2!A:C,3,FALSE),""),VLOOKUP(C89,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Ramadhani Vanva Fauzia</v>
+        <v>0</v>
       </c>
       <c r="C89" s="2">
         <v>1571305354</v>
@@ -4938,9 +4952,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C90)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B90" t="str">
+      <c r="B90">
         <f>IF(A90="Ada",IF(IFERROR(VLOOKUP(C90,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C90,Sheet2!A:C,3,FALSE),""),VLOOKUP(C90,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Stephanie Debora Assa</v>
+        <v>0</v>
       </c>
       <c r="C90" s="2">
         <v>1571305360</v>
@@ -5058,9 +5072,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C93)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B93" t="str">
+      <c r="B93">
         <f>IF(A93="Ada",IF(IFERROR(VLOOKUP(C93,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C93,Sheet2!A:C,3,FALSE),""),VLOOKUP(C93,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>: Juris Vassa Ivandro, S.Kom</v>
+        <v>0</v>
       </c>
       <c r="C93" s="2">
         <v>1571305741</v>
@@ -5218,9 +5232,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C97)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B97" t="str">
+      <c r="B97">
         <f>IF(A97="Ada",IF(IFERROR(VLOOKUP(C97,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C97,Sheet2!A:C,3,FALSE),""),VLOOKUP(C97,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>rais nurwahyudin</v>
+        <v>0</v>
       </c>
       <c r="C97" s="2">
         <v>1571306241</v>
@@ -5258,9 +5272,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C98)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B98">
         <f>IF(A98="Ada",IF(IFERROR(VLOOKUP(C98,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C98,Sheet2!A:C,3,FALSE),""),VLOOKUP(C98,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Muhammad Raya Maulana, S.T</v>
+        <v>0</v>
       </c>
       <c r="C98" s="2">
         <v>1571306264</v>
@@ -5536,11 +5550,11 @@
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C105)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B105" t="str">
+        <v>Ada</v>
+      </c>
+      <c r="B105">
         <f>IF(A105="Ada",IF(IFERROR(VLOOKUP(C105,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C105,Sheet2!A:C,3,FALSE),""),VLOOKUP(C105,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C105" s="2">
         <v>1571307035</v>
@@ -5576,11 +5590,11 @@
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C106)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B106" t="str">
+        <v>Ada</v>
+      </c>
+      <c r="B106">
         <f>IF(A106="Ada",IF(IFERROR(VLOOKUP(C106,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C106,Sheet2!A:C,3,FALSE),""),VLOOKUP(C106,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C106" s="2">
         <v>1571307129</v>
@@ -5618,9 +5632,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C107)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B107" t="str">
+      <c r="B107">
         <f>IF(A107="Ada",IF(IFERROR(VLOOKUP(C107,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C107,Sheet2!A:C,3,FALSE),""),VLOOKUP(C107,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Putri Taqwa Prasetyaningrum</v>
+        <v>0</v>
       </c>
       <c r="C107" s="2">
         <v>1571307383</v>
@@ -5698,9 +5712,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C109)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B109" t="str">
+      <c r="B109">
         <f>IF(A109="Ada",IF(IFERROR(VLOOKUP(C109,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C109,Sheet2!A:C,3,FALSE),""),VLOOKUP(C109,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Fadli Sirait, S.Si, M.T, Ph.D</v>
+        <v>0</v>
       </c>
       <c r="C109" s="2">
         <v>1571307433</v>
@@ -5938,9 +5952,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C115)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B115" t="str">
+      <c r="B115">
         <f>IF(A115="Ada",IF(IFERROR(VLOOKUP(C115,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C115,Sheet2!A:C,3,FALSE),""),VLOOKUP(C115,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Lintang Deni Laksana</v>
+        <v>0</v>
       </c>
       <c r="C115" s="2">
         <v>1571307622</v>
@@ -6138,9 +6152,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C120)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B120" t="str">
+      <c r="B120">
         <f>IF(A120="Ada",IF(IFERROR(VLOOKUP(C120,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C120,Sheet2!A:C,3,FALSE),""),VLOOKUP(C120,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Mohammad Noer Dafiq</v>
+        <v>0</v>
       </c>
       <c r="C120" s="2">
         <v>1571307671</v>
@@ -6178,9 +6192,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C121)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B121" t="str">
+      <c r="B121">
         <f>IF(A121="Ada",IF(IFERROR(VLOOKUP(C121,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C121,Sheet2!A:C,3,FALSE),""),VLOOKUP(C121,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Nurwahid Rahman</v>
+        <v>0</v>
       </c>
       <c r="C121" s="2">
         <v>1571307676</v>
@@ -6336,11 +6350,11 @@
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C125)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B125" t="str">
+        <v>Ada</v>
+      </c>
+      <c r="B125">
         <f>IF(A125="Ada",IF(IFERROR(VLOOKUP(C125,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C125,Sheet2!A:C,3,FALSE),""),VLOOKUP(C125,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C125" s="2">
         <v>1571308850</v>
@@ -6460,7 +6474,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{425A0240-4B53-4571-9694-7E2E7C87F1EF}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -6470,7 +6484,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>1571279780</v>
+        <v>1571267469</v>
       </c>
       <c r="C1" t="s">
         <v>282</v>
@@ -6478,7 +6492,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1571267967</v>
+        <v>1571267484</v>
       </c>
       <c r="B2" t="s">
         <v>258</v>
@@ -6489,7 +6503,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1571294926</v>
+        <v>1571267967</v>
       </c>
       <c r="C3" t="s">
         <v>283</v>
@@ -6497,7 +6511,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1571306264</v>
+        <v>1571268176</v>
       </c>
       <c r="B4" t="s">
         <v>259</v>
@@ -6508,7 +6522,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1571290818</v>
+        <v>1571279780</v>
       </c>
       <c r="C5" t="s">
         <v>284</v>
@@ -6516,7 +6530,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1571307622</v>
+        <v>1571280074</v>
       </c>
       <c r="C6" t="s">
         <v>285</v>
@@ -6524,7 +6538,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1571298976</v>
+        <v>1571281021</v>
       </c>
       <c r="C7" t="s">
         <v>286</v>
@@ -6532,7 +6546,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1571305337</v>
+        <v>1571281084</v>
       </c>
       <c r="B8" t="s">
         <v>260</v>
@@ -6543,7 +6557,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1571290388</v>
+        <v>1571282959</v>
       </c>
       <c r="B9" t="s">
         <v>261</v>
@@ -6554,7 +6568,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1571291668</v>
+        <v>1571286979</v>
       </c>
       <c r="B10" t="s">
         <v>262</v>
@@ -6565,7 +6579,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1571303126</v>
+        <v>1571289829</v>
       </c>
       <c r="B11" t="s">
         <v>263</v>
@@ -6576,7 +6590,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1571282959</v>
+        <v>1571290388</v>
       </c>
       <c r="C12" t="s">
         <v>289</v>
@@ -6584,7 +6598,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1571300706</v>
+        <v>1571290818</v>
       </c>
       <c r="B13" t="s">
         <v>264</v>
@@ -6595,7 +6609,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1571291423</v>
+        <v>1571291272</v>
       </c>
       <c r="C14" t="s">
         <v>290</v>
@@ -6603,7 +6617,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1571307383</v>
+        <v>1571291423</v>
       </c>
       <c r="B15" t="s">
         <v>265</v>
@@ -6614,7 +6628,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1571297897</v>
+        <v>1571291625</v>
       </c>
       <c r="B16" t="s">
         <v>266</v>
@@ -6625,7 +6639,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1571305741</v>
+        <v>1571291638</v>
       </c>
       <c r="C17" t="s">
         <v>293</v>
@@ -6633,7 +6647,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>1571298558</v>
+        <v>1571291668</v>
       </c>
       <c r="C18" t="s">
         <v>294</v>
@@ -6641,7 +6655,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>1571298209</v>
+        <v>1571291877</v>
       </c>
       <c r="C19" t="s">
         <v>295</v>
@@ -6649,7 +6663,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>1571306241</v>
+        <v>1571291935</v>
       </c>
       <c r="C20" t="s">
         <v>296</v>
@@ -6657,7 +6671,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>1571290388</v>
+        <v>1571292356</v>
       </c>
       <c r="B21" t="s">
         <v>267</v>
@@ -6668,7 +6682,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>1571298045</v>
+        <v>1571292417</v>
       </c>
       <c r="C22" t="s">
         <v>298</v>
@@ -6676,7 +6690,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1571296305</v>
+        <v>1571294926</v>
       </c>
       <c r="B23" t="s">
         <v>268</v>
@@ -6687,7 +6701,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1571298458</v>
+        <v>1571295713</v>
       </c>
       <c r="B24" t="s">
         <v>269</v>
@@ -6698,7 +6712,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>1571291935</v>
+        <v>1571296305</v>
       </c>
       <c r="C25" t="s">
         <v>301</v>
@@ -6706,7 +6720,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1571305122</v>
+        <v>1571297897</v>
       </c>
       <c r="B26" t="s">
         <v>270</v>
@@ -6717,7 +6731,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1571305360</v>
+        <v>1571298038</v>
       </c>
       <c r="B27" t="s">
         <v>271</v>
@@ -6728,7 +6742,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>1571291877</v>
+        <v>1571298045</v>
       </c>
       <c r="B28" t="s">
         <v>272</v>
@@ -6739,7 +6753,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1571305354</v>
+        <v>1571298209</v>
       </c>
       <c r="B29" t="s">
         <v>273</v>
@@ -6750,7 +6764,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>1571305199</v>
+        <v>1571298278</v>
       </c>
       <c r="B30" t="s">
         <v>274</v>
@@ -6761,7 +6775,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1571304164</v>
+        <v>1571298458</v>
       </c>
       <c r="B31" t="s">
         <v>275</v>
@@ -6772,7 +6786,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>1571307676</v>
+        <v>1571298558</v>
       </c>
       <c r="B32" t="s">
         <v>276</v>
@@ -6783,7 +6797,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>1571291638</v>
+        <v>1571298976</v>
       </c>
       <c r="C33" t="s">
         <v>307</v>
@@ -6791,7 +6805,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>1571307671</v>
+        <v>1571300264</v>
       </c>
       <c r="B34" t="s">
         <v>277</v>
@@ -6802,7 +6816,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>1571289829</v>
+        <v>1571300636</v>
       </c>
       <c r="C35" t="s">
         <v>309</v>
@@ -6810,7 +6824,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>1571291625</v>
+        <v>1571300706</v>
       </c>
       <c r="B36" t="s">
         <v>278</v>
@@ -6821,7 +6835,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>1571305316</v>
+        <v>1571301191</v>
       </c>
       <c r="C37" t="s">
         <v>311</v>
@@ -6829,7 +6843,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>1571307433</v>
+        <v>1571303126</v>
       </c>
       <c r="C38" t="s">
         <v>312</v>
@@ -6837,7 +6851,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>2524612</v>
+        <v>1571304164</v>
       </c>
       <c r="B39" t="s">
         <v>279</v>
@@ -6848,7 +6862,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>1571300264</v>
+        <v>1571304167</v>
       </c>
       <c r="B40" t="s">
         <v>280</v>
@@ -6859,7 +6873,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>1571304164</v>
+        <v>1571304705</v>
       </c>
       <c r="B41" t="s">
         <v>275</v>
@@ -6870,7 +6884,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>1571297897</v>
+        <v>1571304827</v>
       </c>
       <c r="B42" t="s">
         <v>266</v>
@@ -6881,13 +6895,116 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>1571304167</v>
+        <v>1571305122</v>
       </c>
       <c r="B43" t="s">
         <v>281</v>
       </c>
       <c r="C43" t="s">
         <v>306</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>1571305199</v>
+      </c>
+      <c r="C44" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>1571305279</v>
+      </c>
+      <c r="C45" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>1571305316</v>
+      </c>
+      <c r="B46" t="s">
+        <v>281</v>
+      </c>
+      <c r="C46" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>1571305337</v>
+      </c>
+      <c r="B47" t="s">
+        <v>315</v>
+      </c>
+      <c r="C47" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>1571305354</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>1571305360</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>1571305741</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>1571306241</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>1571306264</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>1571307035</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>1571307129</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>1571307383</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>1571307433</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>1571307622</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>1571307671</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>1571307676</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>1571308850</v>
       </c>
     </row>
   </sheetData>

--- a/Cek Validasi.xlsx
+++ b/Cek Validasi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\icvee\ICVEE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CFBF2C-3F93-4C40-9C6F-8ED85877AF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4114FD-5DDB-4113-ADF2-09124AE49E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9BCEFB9A-EF35-43F1-AD2F-79243D21B5CB}"/>
   </bookViews>
@@ -1035,10 +1035,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1630,11 +1631,11 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C7)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B7" t="str">
         <f>IF(A7="Ada",IF(IFERROR(VLOOKUP(C7,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C7,Sheet2!A:C,3,FALSE),""),VLOOKUP(C7,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Dr. Hendy Briantoro</v>
       </c>
       <c r="C7" s="2">
         <v>1571273336</v>
@@ -1674,7 +1675,7 @@
       </c>
       <c r="B8" t="str">
         <f>IF(A8="Ada",IF(IFERROR(VLOOKUP(C8,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C8,Sheet2!A:C,3,FALSE),""),VLOOKUP(C8,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Dr. Hendy Briantoro</v>
+        <v>Lintang Deni Laksana</v>
       </c>
       <c r="C8" s="2">
         <v>1571279780</v>
@@ -1714,7 +1715,7 @@
       </c>
       <c r="B9" t="str">
         <f>IF(A9="Ada",IF(IFERROR(VLOOKUP(C9,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C9,Sheet2!A:C,3,FALSE),""),VLOOKUP(C9,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Lintang Deni Laksana</v>
+        <v>Mr. Fajar Romadhan</v>
       </c>
       <c r="C9" s="2">
         <v>1571280074</v>
@@ -1750,11 +1751,11 @@
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C10)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B10" t="str">
         <f>IF(A10="Ada",IF(IFERROR(VLOOKUP(C10,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C10,Sheet2!A:C,3,FALSE),""),VLOOKUP(C10,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Mrs. Alya Esa Mentari</v>
       </c>
       <c r="C10" s="2">
         <v>1571280332</v>
@@ -1794,7 +1795,7 @@
       </c>
       <c r="B11" t="str">
         <f>IF(A11="Ada",IF(IFERROR(VLOOKUP(C11,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C11,Sheet2!A:C,3,FALSE),""),VLOOKUP(C11,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Mr. Fajar Romadhan</v>
+        <v>Nathanael Sitanggang; Putri Lynna A Luthan</v>
       </c>
       <c r="C11" s="2">
         <v>1571281021</v>
@@ -1834,7 +1835,7 @@
       </c>
       <c r="B12" t="str">
         <f>IF(A12="Ada",IF(IFERROR(VLOOKUP(C12,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C12,Sheet2!A:C,3,FALSE),""),VLOOKUP(C12,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Mrs. Alya Esa Mentari</v>
+        <v>Annisya Diaz Chandradewi, Dwi Dya Nindasari</v>
       </c>
       <c r="C12" s="2">
         <v>1571281084</v>
@@ -1874,7 +1875,7 @@
       </c>
       <c r="B13" t="str">
         <f>IF(A13="Ada",IF(IFERROR(VLOOKUP(C13,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C13,Sheet2!A:C,3,FALSE),""),VLOOKUP(C13,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Nathanael Sitanggang; Putri Lynna A Luthan</v>
+        <v>Kurnia Chairunnisa</v>
       </c>
       <c r="C13" s="2">
         <v>1571282959</v>
@@ -1954,7 +1955,7 @@
       </c>
       <c r="B15" t="str">
         <f>IF(A15="Ada",IF(IFERROR(VLOOKUP(C15,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C15,Sheet2!A:C,3,FALSE),""),VLOOKUP(C15,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Annisya Diaz Chandradewi, Dwi Dya Nindasari</v>
+        <v>Afandi Sahputra, S.T., M.T.</v>
       </c>
       <c r="C15" s="2">
         <v>1571286979</v>
@@ -2034,7 +2035,7 @@
       </c>
       <c r="B17" t="str">
         <f>IF(A17="Ada",IF(IFERROR(VLOOKUP(C17,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C17,Sheet2!A:C,3,FALSE),""),VLOOKUP(C17,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Kurnia Chairunnisa</v>
+        <v>Albertus Andika Tri Anggoro</v>
       </c>
       <c r="C17" s="2">
         <v>1571289829</v>
@@ -2074,7 +2075,7 @@
       </c>
       <c r="B18" t="str">
         <f>IF(A18="Ada",IF(IFERROR(VLOOKUP(C18,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C18,Sheet2!A:C,3,FALSE),""),VLOOKUP(C18,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Afandi Sahputra, S.T., M.T.</v>
+        <v>Hamid Rahman, M.Kom.</v>
       </c>
       <c r="C18" s="2">
         <v>1571290388</v>
@@ -2154,7 +2155,7 @@
       </c>
       <c r="B20" t="str">
         <f>IF(A20="Ada",IF(IFERROR(VLOOKUP(C20,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C20,Sheet2!A:C,3,FALSE),""),VLOOKUP(C20,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Albertus Andika Tri Anggoro</v>
+        <v>Putri Taqwa Prasetyaningrum</v>
       </c>
       <c r="C20" s="2">
         <v>1571290818</v>
@@ -2274,7 +2275,7 @@
       </c>
       <c r="B23" t="str">
         <f>IF(A23="Ada",IF(IFERROR(VLOOKUP(C23,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C23,Sheet2!A:C,3,FALSE),""),VLOOKUP(C23,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Hamid Rahman, M.Kom.</v>
+        <v>Nanditya Vianti Putri</v>
       </c>
       <c r="C23" s="2">
         <v>1571291272</v>
@@ -2314,7 +2315,7 @@
       </c>
       <c r="B24" t="str">
         <f>IF(A24="Ada",IF(IFERROR(VLOOKUP(C24,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C24,Sheet2!A:C,3,FALSE),""),VLOOKUP(C24,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Putri Taqwa Prasetyaningrum</v>
+        <v>: Juris Vassa Ivandro, S.Kom</v>
       </c>
       <c r="C24" s="2">
         <v>1571291423</v>
@@ -2354,7 +2355,7 @@
       </c>
       <c r="B25" t="str">
         <f>IF(A25="Ada",IF(IFERROR(VLOOKUP(C25,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C25,Sheet2!A:C,3,FALSE),""),VLOOKUP(C25,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Nanditya Vianti Putri</v>
+        <v>Anisa Dzulkarnain, S.Kom., M.Kom.</v>
       </c>
       <c r="C25" s="2">
         <v>1571291625</v>
@@ -2394,7 +2395,7 @@
       </c>
       <c r="B26" t="str">
         <f>IF(A26="Ada",IF(IFERROR(VLOOKUP(C26,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C26,Sheet2!A:C,3,FALSE),""),VLOOKUP(C26,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>: Juris Vassa Ivandro, S.Kom</v>
+        <v>SUGITO, S.Kom</v>
       </c>
       <c r="C26" s="2">
         <v>1571291638</v>
@@ -2434,7 +2435,7 @@
       </c>
       <c r="B27" t="str">
         <f>IF(A27="Ada",IF(IFERROR(VLOOKUP(C27,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C27,Sheet2!A:C,3,FALSE),""),VLOOKUP(C27,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Anisa Dzulkarnain, S.Kom., M.Kom.</v>
+        <v>rais nurwahyudin</v>
       </c>
       <c r="C27" s="2">
         <v>1571291668</v>
@@ -2594,7 +2595,7 @@
       </c>
       <c r="B31" t="str">
         <f>IF(A31="Ada",IF(IFERROR(VLOOKUP(C31,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C31,Sheet2!A:C,3,FALSE),""),VLOOKUP(C31,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>SUGITO, S.Kom</v>
+        <v>Prof. Nathanael Sitanggang; Prof. Putri Lynna A. Luthan</v>
       </c>
       <c r="C31" s="2">
         <v>1571291877</v>
@@ -2674,7 +2675,7 @@
       </c>
       <c r="B33" t="str">
         <f>IF(A33="Ada",IF(IFERROR(VLOOKUP(C33,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C33,Sheet2!A:C,3,FALSE),""),VLOOKUP(C33,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>rais nurwahyudin</v>
+        <v>Sugeng Hari Wibowo</v>
       </c>
       <c r="C33" s="2">
         <v>1571291935</v>
@@ -2954,7 +2955,7 @@
       </c>
       <c r="B40" t="str">
         <f>IF(A40="Ada",IF(IFERROR(VLOOKUP(C40,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C40,Sheet2!A:C,3,FALSE),""),VLOOKUP(C40,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Prof. Nathanael Sitanggang; Prof. Putri Lynna A. Luthan</v>
+        <v>Beny Prasetyo</v>
       </c>
       <c r="C40" s="2">
         <v>1571292356</v>
@@ -3074,7 +3075,7 @@
       </c>
       <c r="B43" t="str">
         <f>IF(A43="Ada",IF(IFERROR(VLOOKUP(C43,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C43,Sheet2!A:C,3,FALSE),""),VLOOKUP(C43,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Sugeng Hari Wibowo</v>
+        <v>Maskur</v>
       </c>
       <c r="C43" s="2">
         <v>1571292417</v>
@@ -3114,7 +3115,7 @@
       </c>
       <c r="B44" t="str">
         <f>IF(A44="Ada",IF(IFERROR(VLOOKUP(C44,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C44,Sheet2!A:C,3,FALSE),""),VLOOKUP(C44,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Beny Prasetyo</v>
+        <v>Fauziyah Wafa'Abdillah, S.Tr.T.</v>
       </c>
       <c r="C44" s="2">
         <v>1571294926</v>
@@ -3194,7 +3195,7 @@
       </c>
       <c r="B46" t="str">
         <f>IF(A46="Ada",IF(IFERROR(VLOOKUP(C46,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C46,Sheet2!A:C,3,FALSE),""),VLOOKUP(C46,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Maskur</v>
+        <v>Putri Christianti Harefa</v>
       </c>
       <c r="C46" s="2">
         <v>1571295713</v>
@@ -3234,7 +3235,7 @@
       </c>
       <c r="B47" t="str">
         <f>IF(A47="Ada",IF(IFERROR(VLOOKUP(C47,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C47,Sheet2!A:C,3,FALSE),""),VLOOKUP(C47,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Fauziyah Wafa'Abdillah, S.Tr.T.</v>
+        <v>Stephanie Debora Assa</v>
       </c>
       <c r="C47" s="2">
         <v>1571296305</v>
@@ -3394,7 +3395,7 @@
       </c>
       <c r="B51" t="str">
         <f>IF(A51="Ada",IF(IFERROR(VLOOKUP(C51,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C51,Sheet2!A:C,3,FALSE),""),VLOOKUP(C51,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Putri Christianti Harefa</v>
+        <v>Veldin A. Talorete Jr.</v>
       </c>
       <c r="C51" s="2">
         <v>1571297897</v>
@@ -3434,7 +3435,7 @@
       </c>
       <c r="B52" t="str">
         <f>IF(A52="Ada",IF(IFERROR(VLOOKUP(C52,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C52,Sheet2!A:C,3,FALSE),""),VLOOKUP(C52,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Stephanie Debora Assa</v>
+        <v>Ramadhani Vanva Fauzia</v>
       </c>
       <c r="C52" s="2">
         <v>1571298038</v>
@@ -3474,7 +3475,7 @@
       </c>
       <c r="B53" t="str">
         <f>IF(A53="Ada",IF(IFERROR(VLOOKUP(C53,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C53,Sheet2!A:C,3,FALSE),""),VLOOKUP(C53,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Veldin A. Talorete Jr.</v>
+        <v>Mifta Nur Farid</v>
       </c>
       <c r="C53" s="2">
         <v>1571298045</v>
@@ -3514,7 +3515,7 @@
       </c>
       <c r="B54" t="str">
         <f>IF(A54="Ada",IF(IFERROR(VLOOKUP(C54,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C54,Sheet2!A:C,3,FALSE),""),VLOOKUP(C54,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Ramadhani Vanva Fauzia</v>
+        <v>Aditya Sheva Pratama</v>
       </c>
       <c r="C54" s="2">
         <v>1571298209</v>
@@ -3594,7 +3595,7 @@
       </c>
       <c r="B56" t="str">
         <f>IF(A56="Ada",IF(IFERROR(VLOOKUP(C56,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C56,Sheet2!A:C,3,FALSE),""),VLOOKUP(C56,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Mifta Nur Farid</v>
+        <v>Nurwahid Rahman</v>
       </c>
       <c r="C56" s="2">
         <v>1571298278</v>
@@ -3670,11 +3671,11 @@
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C58)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B58" t="str">
         <f>IF(A58="Ada",IF(IFERROR(VLOOKUP(C58,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C58,Sheet2!A:C,3,FALSE),""),VLOOKUP(C58,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Eric Julianto</v>
       </c>
       <c r="C58" s="2">
         <v>1571298391</v>
@@ -3714,7 +3715,7 @@
       </c>
       <c r="B59" t="str">
         <f>IF(A59="Ada",IF(IFERROR(VLOOKUP(C59,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C59,Sheet2!A:C,3,FALSE),""),VLOOKUP(C59,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Aditya Sheva Pratama</v>
+        <v>Mohammad Noer Dafiq</v>
       </c>
       <c r="C59" s="2">
         <v>1571298458</v>
@@ -3790,11 +3791,11 @@
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C61)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B61" t="str">
         <f>IF(A61="Ada",IF(IFERROR(VLOOKUP(C61,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C61,Sheet2!A:C,3,FALSE),""),VLOOKUP(C61,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Eko Puji Laksono, S.Kom.,M.Kom</v>
       </c>
       <c r="C61" s="2">
         <v>1571298535</v>
@@ -3830,11 +3831,11 @@
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C62)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B62" t="str">
         <f>IF(A62="Ada",IF(IFERROR(VLOOKUP(C62,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C62,Sheet2!A:C,3,FALSE),""),VLOOKUP(C62,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>DAVE SHANNA MARIE E. GIGAWIN &amp; JOHN PAUL L. ULLEGUE</v>
       </c>
       <c r="C62" s="2">
         <v>1571298550</v>
@@ -3874,7 +3875,7 @@
       </c>
       <c r="B63" t="str">
         <f>IF(A63="Ada",IF(IFERROR(VLOOKUP(C63,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C63,Sheet2!A:C,3,FALSE),""),VLOOKUP(C63,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Nurwahid Rahman</v>
+        <v>Hastupara Amurwojakti</v>
       </c>
       <c r="C63" s="2">
         <v>1571298558</v>
@@ -3994,7 +3995,7 @@
       </c>
       <c r="B66" t="str">
         <f>IF(A66="Ada",IF(IFERROR(VLOOKUP(C66,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C66,Sheet2!A:C,3,FALSE),""),VLOOKUP(C66,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Eric Julianto</v>
+        <v>Fadli Sirait, S.Si, M.T, Ph.D</v>
       </c>
       <c r="C66" s="2">
         <v>1571298976</v>
@@ -4030,11 +4031,11 @@
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C67)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B67" t="str">
         <f>IF(A67="Ada",IF(IFERROR(VLOOKUP(C67,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C67,Sheet2!A:C,3,FALSE),""),VLOOKUP(C67,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>-</v>
       </c>
       <c r="C67" s="2">
         <v>1571299336</v>
@@ -4074,7 +4075,7 @@
       </c>
       <c r="B68" t="str">
         <f>IF(A68="Ada",IF(IFERROR(VLOOKUP(C68,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C68,Sheet2!A:C,3,FALSE),""),VLOOKUP(C68,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Mohammad Noer Dafiq</v>
+        <v>Chandra Restu Pradipto, Aloysius Bernanda Gunawan, Bambang Pratama</v>
       </c>
       <c r="C68" s="2">
         <v>1571300264</v>
@@ -4114,7 +4115,7 @@
       </c>
       <c r="B69" t="str">
         <f>IF(A69="Ada",IF(IFERROR(VLOOKUP(C69,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C69,Sheet2!A:C,3,FALSE),""),VLOOKUP(C69,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Eko Puji Laksono, S.Kom.,M.Kom</v>
+        <v>Aditya Sheva Pratama</v>
       </c>
       <c r="C69" s="2">
         <v>1571300636</v>
@@ -4154,7 +4155,7 @@
       </c>
       <c r="B70" t="str">
         <f>IF(A70="Ada",IF(IFERROR(VLOOKUP(C70,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C70,Sheet2!A:C,3,FALSE),""),VLOOKUP(C70,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>DAVE SHANNA MARIE E. GIGAWIN &amp; JOHN PAUL L. ULLEGUE</v>
+        <v>Nanditya Vianti Putri</v>
       </c>
       <c r="C70" s="2">
         <v>1571300706</v>
@@ -4194,7 +4195,7 @@
       </c>
       <c r="B71" t="str">
         <f>IF(A71="Ada",IF(IFERROR(VLOOKUP(C71,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C71,Sheet2!A:C,3,FALSE),""),VLOOKUP(C71,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Hastupara Amurwojakti</v>
+        <v>Muhammad Fahry Ali</v>
       </c>
       <c r="C71" s="2">
         <v>1571301191</v>
@@ -4274,7 +4275,7 @@
       </c>
       <c r="B73" t="str">
         <f>IF(A73="Ada",IF(IFERROR(VLOOKUP(C73,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C73,Sheet2!A:C,3,FALSE),""),VLOOKUP(C73,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Fadli Sirait, S.Si, M.T, Ph.D</v>
+        <v>Osmalina Nur Rahma, S.T., M.Si.</v>
       </c>
       <c r="C73" s="2">
         <v>1571303126</v>
@@ -4314,7 +4315,7 @@
       </c>
       <c r="B74" t="str">
         <f>IF(A74="Ada",IF(IFERROR(VLOOKUP(C74,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C74,Sheet2!A:C,3,FALSE),""),VLOOKUP(C74,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>-</v>
+        <v>I Gusti bagus Wiraditya</v>
       </c>
       <c r="C74" s="2">
         <v>1571304164</v>
@@ -4354,7 +4355,7 @@
       </c>
       <c r="B75" t="str">
         <f>IF(A75="Ada",IF(IFERROR(VLOOKUP(C75,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C75,Sheet2!A:C,3,FALSE),""),VLOOKUP(C75,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Chandra Restu Pradipto, Aloysius Bernanda Gunawan, Bambang Pratama</v>
+        <v>Muhammad Fahry Ali</v>
       </c>
       <c r="C75" s="2">
         <v>1571304167</v>
@@ -4430,11 +4431,11 @@
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C77)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
+        <v>Ada</v>
       </c>
       <c r="B77" t="str">
         <f>IF(A77="Ada",IF(IFERROR(VLOOKUP(C77,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C77,Sheet2!A:C,3,FALSE),""),VLOOKUP(C77,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>Yan Watequlis Syaifudin</v>
       </c>
       <c r="C77" s="2">
         <v>1571304412</v>
@@ -4512,9 +4513,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C79)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B79">
         <f>IF(A79="Ada",IF(IFERROR(VLOOKUP(C79,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C79,Sheet2!A:C,3,FALSE),""),VLOOKUP(C79,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Aditya Sheva Pratama</v>
+        <v>0</v>
       </c>
       <c r="C79" s="2">
         <v>1571304705</v>
@@ -4552,9 +4553,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C80)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B80" t="str">
+      <c r="B80">
         <f>IF(A80="Ada",IF(IFERROR(VLOOKUP(C80,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C80,Sheet2!A:C,3,FALSE),""),VLOOKUP(C80,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Nanditya Vianti Putri</v>
+        <v>0</v>
       </c>
       <c r="C80" s="2">
         <v>1571304827</v>
@@ -4592,9 +4593,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C81)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B81">
         <f>IF(A81="Ada",IF(IFERROR(VLOOKUP(C81,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C81,Sheet2!A:C,3,FALSE),""),VLOOKUP(C81,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Muhammad Fahry Ali</v>
+        <v>0</v>
       </c>
       <c r="C81" s="2">
         <v>1571305122</v>
@@ -4712,9 +4713,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C84)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B84" t="str">
+      <c r="B84">
         <f>IF(A84="Ada",IF(IFERROR(VLOOKUP(C84,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C84,Sheet2!A:C,3,FALSE),""),VLOOKUP(C84,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Osmalina Nur Rahma, S.T., M.Si.</v>
+        <v>0</v>
       </c>
       <c r="C84" s="2">
         <v>1571305199</v>
@@ -4792,9 +4793,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C86)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B86" t="str">
+      <c r="B86">
         <f>IF(A86="Ada",IF(IFERROR(VLOOKUP(C86,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C86,Sheet2!A:C,3,FALSE),""),VLOOKUP(C86,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>I Gusti bagus Wiraditya</v>
+        <v>0</v>
       </c>
       <c r="C86" s="2">
         <v>1571305279</v>
@@ -4832,9 +4833,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C87)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B87">
         <f>IF(A87="Ada",IF(IFERROR(VLOOKUP(C87,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C87,Sheet2!A:C,3,FALSE),""),VLOOKUP(C87,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Muhammad Fahry Ali</v>
+        <v>0</v>
       </c>
       <c r="C87" s="2">
         <v>1571305316</v>
@@ -4872,9 +4873,9 @@
         <f>IF(COUNTIF(Sheet2!A:A,C88)&gt;0,"Ada","Tidak Ada")</f>
         <v>Ada</v>
       </c>
-      <c r="B88" t="str">
+      <c r="B88">
         <f>IF(A88="Ada",IF(IFERROR(VLOOKUP(C88,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C88,Sheet2!A:C,3,FALSE),""),VLOOKUP(C88,Sheet2!A:C,2,FALSE)),"")</f>
-        <v>Yan Watequlis Syaifudin</v>
+        <v>0</v>
       </c>
       <c r="C88" s="2">
         <v>1571305337</v>
@@ -5350,11 +5351,11 @@
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C100)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B100" t="str">
+        <v>Ada</v>
+      </c>
+      <c r="B100">
         <f>IF(A100="Ada",IF(IFERROR(VLOOKUP(C100,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C100,Sheet2!A:C,3,FALSE),""),VLOOKUP(C100,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C100" s="2">
         <v>1571306279</v>
@@ -5670,11 +5671,11 @@
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C108)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B108" t="str">
+        <v>Ada</v>
+      </c>
+      <c r="B108">
         <f>IF(A108="Ada",IF(IFERROR(VLOOKUP(C108,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C108,Sheet2!A:C,3,FALSE),""),VLOOKUP(C108,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C108" s="2">
         <v>1571307415</v>
@@ -6310,11 +6311,11 @@
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C124)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B124" t="str">
+        <v>Ada</v>
+      </c>
+      <c r="B124">
         <f>IF(A124="Ada",IF(IFERROR(VLOOKUP(C124,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C124,Sheet2!A:C,3,FALSE),""),VLOOKUP(C124,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C124" s="2">
         <v>1571308724</v>
@@ -6390,11 +6391,11 @@
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="str">
         <f>IF(COUNTIF(Sheet2!A:A,C126)&gt;0,"Ada","Tidak Ada")</f>
-        <v>Tidak Ada</v>
-      </c>
-      <c r="B126" t="str">
+        <v>Ada</v>
+      </c>
+      <c r="B126">
         <f>IF(A126="Ada",IF(IFERROR(VLOOKUP(C126,Sheet2!A:C,2,FALSE),"")="",IFERROR(VLOOKUP(C126,Sheet2!A:C,3,FALSE),""),VLOOKUP(C126,Sheet2!A:C,2,FALSE)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C126" s="2">
         <v>1571309340</v>
@@ -6474,7 +6475,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{425A0240-4B53-4571-9694-7E2E7C87F1EF}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -6483,7 +6484,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1">
+      <c r="A1" s="3">
         <v>1571267469</v>
       </c>
       <c r="C1" t="s">
@@ -6522,7 +6523,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1571279780</v>
+        <v>1571273336</v>
       </c>
       <c r="C5" t="s">
         <v>284</v>
@@ -6530,7 +6531,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1571280074</v>
+        <v>1571279780</v>
       </c>
       <c r="C6" t="s">
         <v>285</v>
@@ -6538,7 +6539,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1571281021</v>
+        <v>1571280074</v>
       </c>
       <c r="C7" t="s">
         <v>286</v>
@@ -6546,7 +6547,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1571281084</v>
+        <v>1571280332</v>
       </c>
       <c r="B8" t="s">
         <v>260</v>
@@ -6557,7 +6558,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1571282959</v>
+        <v>1571281021</v>
       </c>
       <c r="B9" t="s">
         <v>261</v>
@@ -6568,7 +6569,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1571286979</v>
+        <v>1571281084</v>
       </c>
       <c r="B10" t="s">
         <v>262</v>
@@ -6579,7 +6580,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1571289829</v>
+        <v>1571282959</v>
       </c>
       <c r="B11" t="s">
         <v>263</v>
@@ -6590,7 +6591,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1571290388</v>
+        <v>1571286979</v>
       </c>
       <c r="C12" t="s">
         <v>289</v>
@@ -6598,7 +6599,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1571290818</v>
+        <v>1571289829</v>
       </c>
       <c r="B13" t="s">
         <v>264</v>
@@ -6609,7 +6610,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1571291272</v>
+        <v>1571290388</v>
       </c>
       <c r="C14" t="s">
         <v>290</v>
@@ -6617,7 +6618,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1571291423</v>
+        <v>1571290818</v>
       </c>
       <c r="B15" t="s">
         <v>265</v>
@@ -6628,7 +6629,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1571291625</v>
+        <v>1571291272</v>
       </c>
       <c r="B16" t="s">
         <v>266</v>
@@ -6639,7 +6640,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1571291638</v>
+        <v>1571291423</v>
       </c>
       <c r="C17" t="s">
         <v>293</v>
@@ -6647,7 +6648,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>1571291668</v>
+        <v>1571291625</v>
       </c>
       <c r="C18" t="s">
         <v>294</v>
@@ -6655,7 +6656,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>1571291877</v>
+        <v>1571291638</v>
       </c>
       <c r="C19" t="s">
         <v>295</v>
@@ -6663,7 +6664,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>1571291935</v>
+        <v>1571291668</v>
       </c>
       <c r="C20" t="s">
         <v>296</v>
@@ -6671,7 +6672,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>1571292356</v>
+        <v>1571291877</v>
       </c>
       <c r="B21" t="s">
         <v>267</v>
@@ -6682,7 +6683,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>1571292417</v>
+        <v>1571291935</v>
       </c>
       <c r="C22" t="s">
         <v>298</v>
@@ -6690,7 +6691,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1571294926</v>
+        <v>1571292356</v>
       </c>
       <c r="B23" t="s">
         <v>268</v>
@@ -6701,7 +6702,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1571295713</v>
+        <v>1571292417</v>
       </c>
       <c r="B24" t="s">
         <v>269</v>
@@ -6712,7 +6713,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>1571296305</v>
+        <v>1571294926</v>
       </c>
       <c r="C25" t="s">
         <v>301</v>
@@ -6720,7 +6721,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1571297897</v>
+        <v>1571295713</v>
       </c>
       <c r="B26" t="s">
         <v>270</v>
@@ -6731,7 +6732,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1571298038</v>
+        <v>1571296305</v>
       </c>
       <c r="B27" t="s">
         <v>271</v>
@@ -6742,7 +6743,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>1571298045</v>
+        <v>1571297897</v>
       </c>
       <c r="B28" t="s">
         <v>272</v>
@@ -6753,7 +6754,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1571298209</v>
+        <v>1571298038</v>
       </c>
       <c r="B29" t="s">
         <v>273</v>
@@ -6764,7 +6765,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>1571298278</v>
+        <v>1571298045</v>
       </c>
       <c r="B30" t="s">
         <v>274</v>
@@ -6775,7 +6776,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>1571298458</v>
+        <v>1571298209</v>
       </c>
       <c r="B31" t="s">
         <v>275</v>
@@ -6786,7 +6787,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>1571298558</v>
+        <v>1571298278</v>
       </c>
       <c r="B32" t="s">
         <v>276</v>
@@ -6797,7 +6798,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>1571298976</v>
+        <v>1571298391</v>
       </c>
       <c r="C33" t="s">
         <v>307</v>
@@ -6805,7 +6806,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>1571300264</v>
+        <v>1571298458</v>
       </c>
       <c r="B34" t="s">
         <v>277</v>
@@ -6816,7 +6817,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>1571300636</v>
+        <v>1571298535</v>
       </c>
       <c r="C35" t="s">
         <v>309</v>
@@ -6824,7 +6825,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>1571300706</v>
+        <v>1571298550</v>
       </c>
       <c r="B36" t="s">
         <v>278</v>
@@ -6835,7 +6836,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>1571301191</v>
+        <v>1571298558</v>
       </c>
       <c r="C37" t="s">
         <v>311</v>
@@ -6843,7 +6844,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>1571303126</v>
+        <v>1571298976</v>
       </c>
       <c r="C38" t="s">
         <v>312</v>
@@ -6851,7 +6852,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>1571304164</v>
+        <v>1571299336</v>
       </c>
       <c r="B39" t="s">
         <v>279</v>
@@ -6862,7 +6863,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>1571304167</v>
+        <v>1571300264</v>
       </c>
       <c r="B40" t="s">
         <v>280</v>
@@ -6873,7 +6874,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>1571304705</v>
+        <v>1571300636</v>
       </c>
       <c r="B41" t="s">
         <v>275</v>
@@ -6884,7 +6885,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>1571304827</v>
+        <v>1571300706</v>
       </c>
       <c r="B42" t="s">
         <v>266</v>
@@ -6895,7 +6896,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>1571305122</v>
+        <v>1571301191</v>
       </c>
       <c r="B43" t="s">
         <v>281</v>
@@ -6906,7 +6907,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>1571305199</v>
+        <v>1571303126</v>
       </c>
       <c r="C44" t="s">
         <v>316</v>
@@ -6914,7 +6915,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>1571305279</v>
+        <v>1571304164</v>
       </c>
       <c r="C45" t="s">
         <v>317</v>
@@ -6922,7 +6923,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>1571305316</v>
+        <v>1571304167</v>
       </c>
       <c r="B46" t="s">
         <v>281</v>
@@ -6933,7 +6934,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>1571305337</v>
+        <v>1571304412</v>
       </c>
       <c r="B47" t="s">
         <v>315</v>
@@ -6944,67 +6945,122 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>1571305354</v>
+        <v>1571304705</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>1571305360</v>
+        <v>1571304827</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>1571305741</v>
+        <v>1571305122</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>1571306241</v>
+        <v>1571305199</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>1571306264</v>
+        <v>1571305279</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>1571307035</v>
+        <v>1571305316</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>1571307129</v>
+        <v>1571305337</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>1571307383</v>
+        <v>1571305354</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>1571307433</v>
+        <v>1571305360</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>1571307622</v>
+        <v>1571305741</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>1571307671</v>
+        <v>1571306241</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>1571307676</v>
+        <v>1571306264</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60">
+        <v>1571306279</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>1571307035</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>1571307129</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>1571307383</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>1571307415</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1571307433</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>1571307622</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>1571307671</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>1571307676</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>1571308724</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70">
         <v>1571308850</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>1571309340</v>
       </c>
     </row>
   </sheetData>
